--- a/docs/test/selenium_error.xlsx
+++ b/docs/test/selenium_error.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error Trace Log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Map" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Error Trace Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Traceability Map" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23 16:02:24</t>
+          <t>2026-07-23 23:01:07</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7089,7 @@
       </c>
       <c r="H168" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="H170" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="H171" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="H172" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="H173" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="H174" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="H175" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="H178" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="H202" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (ADMIN role, /admin/users): Resolved URL: http://localhost:3001/admin/users</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="H209" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="H210" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="H211" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="H212" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="H213" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9169,7 @@
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="H225" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="H226" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9449,7 +9449,7 @@
       </c>
       <c r="H227" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="H228" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="H229" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="H230" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="H231" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="H232" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="H233" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="H234" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="H235" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="H236" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="H237" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="H238" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="H239" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="H240" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="H241" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="H242" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="H243" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="H244" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="H245" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="H246" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="H247" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="H248" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="H249" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="H250" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="H251" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="H252" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10489,7 +10489,7 @@
       </c>
       <c r="H253" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="H254" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="H255" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="H256" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="H257" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="H258" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="H259" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10769,7 +10769,7 @@
       </c>
       <c r="H260" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="H261" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10849,7 +10849,7 @@
       </c>
       <c r="H262" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="H263" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="H264" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -10969,7 +10969,7 @@
       </c>
       <c r="H265" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="H266" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="H267" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11089,7 @@
       </c>
       <c r="H268" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="H269" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="H270" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="H271" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11249,7 +11249,7 @@
       </c>
       <c r="H272" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H273" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11329,7 +11329,7 @@
       </c>
       <c r="H274" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="H275" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="H276" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="H277" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="H278" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H279" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="H280" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="H281" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="H282" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="H283" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="H284" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="H285" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="H286" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="H287" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11889,7 +11889,7 @@
       </c>
       <c r="H288" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="H289" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -11969,7 +11969,7 @@
       </c>
       <c r="H290" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="H291" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="H292" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="H293" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="H294" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="H295" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="H296" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="H297" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="H298" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="H299" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="H300" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12409,7 +12409,7 @@
       </c>
       <c r="H301" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="H302" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12489,7 +12489,7 @@
       </c>
       <c r="H303" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="H304" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="H305" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="H306" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="H307" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="H308" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="H309" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="H310" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="H311" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12849,7 +12849,7 @@
       </c>
       <c r="H312" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12889,7 +12889,7 @@
       </c>
       <c r="H313" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="H314" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="H315" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13009,7 +13009,7 @@
       </c>
       <c r="H316" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="H317" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13089,7 +13089,7 @@
       </c>
       <c r="H318" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="H319" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="H320" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="H321" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="H322" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="H323" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="H324" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13369,7 +13369,7 @@
       </c>
       <c r="H325" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="H326" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13449,7 +13449,7 @@
       </c>
       <c r="H327" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13489,7 +13489,7 @@
       </c>
       <c r="H328" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13529,7 +13529,7 @@
       </c>
       <c r="H329" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
       </c>
       <c r="H330" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="H331" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="H332" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13689,7 +13689,7 @@
       </c>
       <c r="H333" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H334" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="H335" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="H336" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13849,7 +13849,7 @@
       </c>
       <c r="H337" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="H338" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="H339" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H340" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="H341" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="H342" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="H343" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="H344" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14169,7 @@
       </c>
       <c r="H345" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="H346" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14249,7 +14249,7 @@
       </c>
       <c r="H347" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="H348" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="H349" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="H350" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="H351" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14449,7 +14449,7 @@
       </c>
       <c r="H352" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14489,7 +14489,7 @@
       </c>
       <c r="H353" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14529,7 +14529,7 @@
       </c>
       <c r="H354" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="H355" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="H356" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="H357" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14689,7 +14689,7 @@
       </c>
       <c r="H358" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="H359" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14769,7 +14769,7 @@
       </c>
       <c r="H360" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="H361" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="H362" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14889,7 +14889,7 @@
       </c>
       <c r="H363" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="H364" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="H365" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="H366" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="H367" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15089,7 +15089,7 @@
       </c>
       <c r="H368" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15129,7 +15129,7 @@
       </c>
       <c r="H369" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15169,7 +15169,7 @@
       </c>
       <c r="H370" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="H371" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15249,7 +15249,7 @@
       </c>
       <c r="H372" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15289,7 +15289,7 @@
       </c>
       <c r="H373" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="H374" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="H375" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="H376" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15449,7 +15449,7 @@
       </c>
       <c r="H377" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="H378" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="H379" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="H380" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="H381" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="H382" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
       </c>
       <c r="H383" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="H384" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15769,7 +15769,7 @@
       </c>
       <c r="H385" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="H386" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="H387" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15889,7 +15889,7 @@
       </c>
       <c r="H388" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="H389" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="H390" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16009,7 +16009,7 @@
       </c>
       <c r="H391" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16049,7 +16049,7 @@
       </c>
       <c r="H392" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16089,7 +16089,7 @@
       </c>
       <c r="H393" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16129,7 +16129,7 @@
       </c>
       <c r="H394" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16169,7 +16169,7 @@
       </c>
       <c r="H395" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="H396" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16249,7 +16249,7 @@
       </c>
       <c r="H397" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="H398" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="H399" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="H400" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H401" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="H402" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="H403" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16529,7 +16529,7 @@
       </c>
       <c r="H404" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="H405" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="H406" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
       </c>
       <c r="H407" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16689,7 +16689,7 @@
       </c>
       <c r="H408" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /admin/products): Resolved URL: http://localhost:3001/admin/products</t>
         </is>
       </c>
     </row>
@@ -16729,7 +16729,7 @@
       </c>
       <c r="H409" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -16769,7 +16769,7 @@
       </c>
       <c r="H410" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="H411" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="H412" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="H413" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="H414" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
       </c>
       <c r="H415" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="H416" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="H417" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="H418" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17129,7 +17129,7 @@
       </c>
       <c r="H419" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17169,7 +17169,7 @@
       </c>
       <c r="H420" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="H421" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="H422" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="H423" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17329,7 +17329,7 @@
       </c>
       <c r="H424" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="H425" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="H426" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17449,7 +17449,7 @@
       </c>
       <c r="H427" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17489,7 +17489,7 @@
       </c>
       <c r="H428" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17529,7 +17529,7 @@
       </c>
       <c r="H429" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17569,7 +17569,7 @@
       </c>
       <c r="H430" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
       </c>
       <c r="H431" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="H432" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="H433" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="H434" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="H435" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="H436" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="H437" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="H438" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="H439" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -17969,7 +17969,7 @@
       </c>
       <c r="H440" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18009,7 +18009,7 @@
       </c>
       <c r="H441" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="H442" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="H443" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="H444" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18169,7 +18169,7 @@
       </c>
       <c r="H445" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18209,7 +18209,7 @@
       </c>
       <c r="H446" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
       </c>
       <c r="H447" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18289,7 +18289,7 @@
       </c>
       <c r="H448" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18329,7 +18329,7 @@
       </c>
       <c r="H449" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="H450" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="H451" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="H452" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18489,7 +18489,7 @@
       </c>
       <c r="H453" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18529,7 +18529,7 @@
       </c>
       <c r="H454" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="H455" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="H456" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="H457" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="H458" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="H459" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18769,7 +18769,7 @@
       </c>
       <c r="H460" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="H461" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H462" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="H463" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="H464" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="H465" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="H466" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="H467" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19089,7 +19089,7 @@
       </c>
       <c r="H468" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19129,7 +19129,7 @@
       </c>
       <c r="H469" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19169,7 +19169,7 @@
       </c>
       <c r="H470" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="H471" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19249,7 +19249,7 @@
       </c>
       <c r="H472" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="H473" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="H474" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="H475" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="H476" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="H477" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="H478" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19529,7 +19529,7 @@
       </c>
       <c r="H479" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19569,7 +19569,7 @@
       </c>
       <c r="H480" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="H481" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="H482" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="H483" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="H484" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19769,7 +19769,7 @@
       </c>
       <c r="H485" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="H486" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
       </c>
       <c r="H487" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="H488" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19929,7 +19929,7 @@
       </c>
       <c r="H489" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -19969,7 +19969,7 @@
       </c>
       <c r="H490" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="H491" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20049,7 +20049,7 @@
       </c>
       <c r="H492" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20089,7 +20089,7 @@
       </c>
       <c r="H493" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20129,7 +20129,7 @@
       </c>
       <c r="H494" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="H495" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="H496" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="H497" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="H498" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20329,7 +20329,7 @@
       </c>
       <c r="H499" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20369,7 +20369,7 @@
       </c>
       <c r="H500" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="H501" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20449,7 +20449,7 @@
       </c>
       <c r="H502" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="H503" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="H504" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="H505" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="H506" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20649,7 +20649,7 @@
       </c>
       <c r="H507" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20689,7 +20689,7 @@
       </c>
       <c r="H508" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="H509" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20769,7 +20769,7 @@
       </c>
       <c r="H510" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="H511" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="H512" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="H513" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20929,7 +20929,7 @@
       </c>
       <c r="H514" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -20969,7 +20969,7 @@
       </c>
       <c r="H515" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="H516" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="H517" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -21089,7 +21089,7 @@
       </c>
       <c r="H518" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -21129,7 +21129,7 @@
       </c>
       <c r="H519" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -21169,7 +21169,7 @@
       </c>
       <c r="H520" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -21209,7 +21209,7 @@
       </c>
       <c r="H521" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -21249,7 +21249,7 @@
       </c>
       <c r="H522" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H523" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="H524" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -21369,7 +21369,7 @@
       </c>
       <c r="H525" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -21409,7 +21409,7 @@
       </c>
       <c r="H526" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/receipts): Resolved URL: http://localhost:3001/inbound/receipts</t>
         </is>
       </c>
     </row>
@@ -21449,7 +21449,7 @@
       </c>
       <c r="H527" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="H528" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="H529" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="H530" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="H531" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21649,7 +21649,7 @@
       </c>
       <c r="H532" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="H533" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21729,7 +21729,7 @@
       </c>
       <c r="H534" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="H535" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21809,7 +21809,7 @@
       </c>
       <c r="H536" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21849,7 +21849,7 @@
       </c>
       <c r="H537" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21889,7 +21889,7 @@
       </c>
       <c r="H538" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="H539" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -21969,7 +21969,7 @@
       </c>
       <c r="H540" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22009,7 +22009,7 @@
       </c>
       <c r="H541" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22049,7 +22049,7 @@
       </c>
       <c r="H542" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="H543" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22129,7 +22129,7 @@
       </c>
       <c r="H544" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22169,7 +22169,7 @@
       </c>
       <c r="H545" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="H546" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22249,7 +22249,7 @@
       </c>
       <c r="H547" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22289,7 +22289,7 @@
       </c>
       <c r="H548" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="H549" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="H550" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="H551" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="H552" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22489,7 +22489,7 @@
       </c>
       <c r="H553" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22529,7 +22529,7 @@
       </c>
       <c r="H554" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22569,7 +22569,7 @@
       </c>
       <c r="H555" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="H556" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22649,7 +22649,7 @@
       </c>
       <c r="H557" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22689,7 +22689,7 @@
       </c>
       <c r="H558" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="H559" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22769,7 +22769,7 @@
       </c>
       <c r="H560" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22809,7 +22809,7 @@
       </c>
       <c r="H561" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22849,7 +22849,7 @@
       </c>
       <c r="H562" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22889,7 +22889,7 @@
       </c>
       <c r="H563" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22929,7 +22929,7 @@
       </c>
       <c r="H564" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -22969,7 +22969,7 @@
       </c>
       <c r="H565" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23009,7 +23009,7 @@
       </c>
       <c r="H566" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23049,7 +23049,7 @@
       </c>
       <c r="H567" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="H568" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="H569" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23169,7 +23169,7 @@
       </c>
       <c r="H570" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23209,7 +23209,7 @@
       </c>
       <c r="H571" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23249,7 +23249,7 @@
       </c>
       <c r="H572" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23289,7 +23289,7 @@
       </c>
       <c r="H573" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23329,7 +23329,7 @@
       </c>
       <c r="H574" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23369,7 +23369,7 @@
       </c>
       <c r="H575" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23409,7 +23409,7 @@
       </c>
       <c r="H576" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23449,7 +23449,7 @@
       </c>
       <c r="H577" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23489,7 +23489,7 @@
       </c>
       <c r="H578" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23529,7 +23529,7 @@
       </c>
       <c r="H579" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23569,7 +23569,7 @@
       </c>
       <c r="H580" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23609,7 +23609,7 @@
       </c>
       <c r="H581" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="H582" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23689,7 +23689,7 @@
       </c>
       <c r="H583" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23729,7 +23729,7 @@
       </c>
       <c r="H584" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23769,7 +23769,7 @@
       </c>
       <c r="H585" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23809,7 +23809,7 @@
       </c>
       <c r="H586" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="H587" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23889,7 +23889,7 @@
       </c>
       <c r="H588" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23929,7 +23929,7 @@
       </c>
       <c r="H589" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -23969,7 +23969,7 @@
       </c>
       <c r="H590" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24009,7 +24009,7 @@
       </c>
       <c r="H591" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24049,7 +24049,7 @@
       </c>
       <c r="H592" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24089,7 +24089,7 @@
       </c>
       <c r="H593" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="H594" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="H595" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24209,7 +24209,7 @@
       </c>
       <c r="H596" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24249,7 +24249,7 @@
       </c>
       <c r="H597" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24289,7 +24289,7 @@
       </c>
       <c r="H598" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24329,7 +24329,7 @@
       </c>
       <c r="H599" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24369,7 +24369,7 @@
       </c>
       <c r="H600" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24409,7 +24409,7 @@
       </c>
       <c r="H601" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24449,7 +24449,7 @@
       </c>
       <c r="H602" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24489,7 +24489,7 @@
       </c>
       <c r="H603" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24529,7 +24529,7 @@
       </c>
       <c r="H604" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="H605" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="H606" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="H607" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="H608" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24729,7 +24729,7 @@
       </c>
       <c r="H609" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24769,7 +24769,7 @@
       </c>
       <c r="H610" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24809,7 +24809,7 @@
       </c>
       <c r="H611" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24849,7 +24849,7 @@
       </c>
       <c r="H612" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24889,7 +24889,7 @@
       </c>
       <c r="H613" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="H614" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -24969,7 +24969,7 @@
       </c>
       <c r="H615" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25009,7 +25009,7 @@
       </c>
       <c r="H616" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25049,7 +25049,7 @@
       </c>
       <c r="H617" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25089,7 +25089,7 @@
       </c>
       <c r="H618" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25129,7 +25129,7 @@
       </c>
       <c r="H619" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="H620" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="H621" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25249,7 @@
       </c>
       <c r="H622" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25289,7 +25289,7 @@
       </c>
       <c r="H623" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25329,7 +25329,7 @@
       </c>
       <c r="H624" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="H625" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25409,7 +25409,7 @@
       </c>
       <c r="H626" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25449,7 +25449,7 @@
       </c>
       <c r="H627" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25489,7 +25489,7 @@
       </c>
       <c r="H628" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25529,7 +25529,7 @@
       </c>
       <c r="H629" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25569,7 +25569,7 @@
       </c>
       <c r="H630" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25609,7 +25609,7 @@
       </c>
       <c r="H631" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="H632" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="H633" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="H634" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="H635" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25809,7 +25809,7 @@
       </c>
       <c r="H636" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25849,7 +25849,7 @@
       </c>
       <c r="H637" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25889,7 +25889,7 @@
       </c>
       <c r="H638" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25929,7 +25929,7 @@
       </c>
       <c r="H639" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="H640" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26009,7 +26009,7 @@
       </c>
       <c r="H641" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26049,7 +26049,7 @@
       </c>
       <c r="H642" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="H643" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="H644" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H645" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26209,7 +26209,7 @@
       </c>
       <c r="H646" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="H647" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26289,7 +26289,7 @@
       </c>
       <c r="H648" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26329,7 +26329,7 @@
       </c>
       <c r="H649" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26369,7 +26369,7 @@
       </c>
       <c r="H650" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26409,7 @@
       </c>
       <c r="H651" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26449,7 +26449,7 @@
       </c>
       <c r="H652" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26489,7 +26489,7 @@
       </c>
       <c r="H653" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="H654" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26569,7 +26569,7 @@
       </c>
       <c r="H655" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26609,7 +26609,7 @@
       </c>
       <c r="H656" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26649,7 +26649,7 @@
       </c>
       <c r="H657" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="H658" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26729,7 +26729,7 @@
       </c>
       <c r="H659" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /outbound/delivery-orders): Resolved URL: http://localhost:3001/outbound/delivery-orders</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="H660" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -26809,7 +26809,7 @@
       </c>
       <c r="H661" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -26849,7 +26849,7 @@
       </c>
       <c r="H662" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -26889,7 +26889,7 @@
       </c>
       <c r="H663" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -26929,7 +26929,7 @@
       </c>
       <c r="H664" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -26969,7 +26969,7 @@
       </c>
       <c r="H665" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27009,7 +27009,7 @@
       </c>
       <c r="H666" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27049,7 +27049,7 @@
       </c>
       <c r="H667" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="H668" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27129,7 +27129,7 @@
       </c>
       <c r="H669" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27169,7 +27169,7 @@
       </c>
       <c r="H670" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27209,7 +27209,7 @@
       </c>
       <c r="H671" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27249,7 +27249,7 @@
       </c>
       <c r="H672" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="H673" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27329,7 +27329,7 @@
       </c>
       <c r="H674" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27369,7 +27369,7 @@
       </c>
       <c r="H675" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27409,7 +27409,7 @@
       </c>
       <c r="H676" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="H677" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27489,7 +27489,7 @@
       </c>
       <c r="H678" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27529,7 +27529,7 @@
       </c>
       <c r="H679" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27569,7 +27569,7 @@
       </c>
       <c r="H680" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="H681" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="H682" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27689,7 +27689,7 @@
       </c>
       <c r="H683" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27729,7 +27729,7 @@
       </c>
       <c r="H684" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="H685" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="H686" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27849,7 +27849,7 @@
       </c>
       <c r="H687" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27889,7 +27889,7 @@
       </c>
       <c r="H688" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27929,7 +27929,7 @@
       </c>
       <c r="H689" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -27969,7 +27969,7 @@
       </c>
       <c r="H690" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28009,7 +28009,7 @@
       </c>
       <c r="H691" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28049,7 +28049,7 @@
       </c>
       <c r="H692" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28089,7 +28089,7 @@
       </c>
       <c r="H693" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28129,7 +28129,7 @@
       </c>
       <c r="H694" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28169,7 +28169,7 @@
       </c>
       <c r="H695" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28209,7 +28209,7 @@
       </c>
       <c r="H696" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28249,7 +28249,7 @@
       </c>
       <c r="H697" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28289,7 +28289,7 @@
       </c>
       <c r="H698" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="H699" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28369,7 +28369,7 @@
       </c>
       <c r="H700" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28409,7 +28409,7 @@
       </c>
       <c r="H701" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="H702" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28489,7 +28489,7 @@
       </c>
       <c r="H703" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="H704" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28569,7 +28569,7 @@
       </c>
       <c r="H705" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28609,7 +28609,7 @@
       </c>
       <c r="H706" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28649,7 +28649,7 @@
       </c>
       <c r="H707" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28689,7 +28689,7 @@
       </c>
       <c r="H708" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28729,7 +28729,7 @@
       </c>
       <c r="H709" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28769,7 +28769,7 @@
       </c>
       <c r="H710" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28809,7 +28809,7 @@
       </c>
       <c r="H711" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="H712" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28889,7 +28889,7 @@
       </c>
       <c r="H713" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28929,7 +28929,7 @@
       </c>
       <c r="H714" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="H715" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29009,7 +29009,7 @@
       </c>
       <c r="H716" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29049,7 +29049,7 @@
       </c>
       <c r="H717" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29089,7 +29089,7 @@
       </c>
       <c r="H718" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29129,7 +29129,7 @@
       </c>
       <c r="H719" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="H720" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29209,7 +29209,7 @@
       </c>
       <c r="H721" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29249,7 +29249,7 @@
       </c>
       <c r="H722" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29289,7 +29289,7 @@
       </c>
       <c r="H723" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29329,7 +29329,7 @@
       </c>
       <c r="H724" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="H725" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29409,7 +29409,7 @@
       </c>
       <c r="H726" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="H727" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29489,7 +29489,7 @@
       </c>
       <c r="H728" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29529,7 +29529,7 @@
       </c>
       <c r="H729" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29569,7 +29569,7 @@
       </c>
       <c r="H730" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29609,7 +29609,7 @@
       </c>
       <c r="H731" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29649,7 +29649,7 @@
       </c>
       <c r="H732" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29689,7 +29689,7 @@
       </c>
       <c r="H733" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29729,7 +29729,7 @@
       </c>
       <c r="H734" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29769,7 +29769,7 @@
       </c>
       <c r="H735" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29809,7 +29809,7 @@
       </c>
       <c r="H736" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29849,7 +29849,7 @@
       </c>
       <c r="H737" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29889,7 +29889,7 @@
       </c>
       <c r="H738" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29929,7 +29929,7 @@
       </c>
       <c r="H739" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="H740" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -30009,7 +30009,7 @@
       </c>
       <c r="H741" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -30049,7 +30049,7 @@
       </c>
       <c r="H742" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -30089,7 +30089,7 @@
       </c>
       <c r="H743" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -30129,7 +30129,7 @@
       </c>
       <c r="H744" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -30169,7 +30169,7 @@
       </c>
       <c r="H745" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -30209,7 +30209,7 @@
       </c>
       <c r="H746" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -30249,7 +30249,7 @@
       </c>
       <c r="H747" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -30289,7 +30289,7 @@
       </c>
       <c r="H748" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -30329,7 +30329,7 @@
       </c>
       <c r="H749" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /transfers/requests): Resolved URL: http://localhost:3001/transfers/requests</t>
         </is>
       </c>
     </row>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="H750" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="H751" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30449,7 +30449,7 @@
       </c>
       <c r="H752" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30489,7 +30489,7 @@
       </c>
       <c r="H753" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30529,7 +30529,7 @@
       </c>
       <c r="H754" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="H755" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30609,7 +30609,7 @@
       </c>
       <c r="H756" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30649,7 +30649,7 @@
       </c>
       <c r="H757" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="H758" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30729,7 +30729,7 @@
       </c>
       <c r="H759" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30769,7 +30769,7 @@
       </c>
       <c r="H760" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30809,7 +30809,7 @@
       </c>
       <c r="H761" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30849,7 +30849,7 @@
       </c>
       <c r="H762" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30889,7 +30889,7 @@
       </c>
       <c r="H763" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30929,7 +30929,7 @@
       </c>
       <c r="H764" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -30969,7 +30969,7 @@
       </c>
       <c r="H765" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31009,7 +31009,7 @@
       </c>
       <c r="H766" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="H767" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31089,7 +31089,7 @@
       </c>
       <c r="H768" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31129,7 +31129,7 @@
       </c>
       <c r="H769" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31169,7 +31169,7 @@
       </c>
       <c r="H770" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31209,7 +31209,7 @@
       </c>
       <c r="H771" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31249,7 +31249,7 @@
       </c>
       <c r="H772" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31289,7 +31289,7 @@
       </c>
       <c r="H773" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31329,7 +31329,7 @@
       </c>
       <c r="H774" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31369,7 +31369,7 @@
       </c>
       <c r="H775" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="H776" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="H777" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="H778" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31529,7 +31529,7 @@
       </c>
       <c r="H779" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31569,7 +31569,7 @@
       </c>
       <c r="H780" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31609,7 +31609,7 @@
       </c>
       <c r="H781" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31649,7 +31649,7 @@
       </c>
       <c r="H782" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31689,7 +31689,7 @@
       </c>
       <c r="H783" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31729,7 +31729,7 @@
       </c>
       <c r="H784" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31769,7 +31769,7 @@
       </c>
       <c r="H785" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31809,7 +31809,7 @@
       </c>
       <c r="H786" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31849,7 +31849,7 @@
       </c>
       <c r="H787" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31889,7 +31889,7 @@
       </c>
       <c r="H788" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31929,7 +31929,7 @@
       </c>
       <c r="H789" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="H790" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -32009,7 +32009,7 @@
       </c>
       <c r="H791" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -32049,7 +32049,7 @@
       </c>
       <c r="H792" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /stocktake): Resolved URL: http://localhost:3001/stocktake</t>
         </is>
       </c>
     </row>
@@ -32089,7 +32089,7 @@
       </c>
       <c r="H793" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="H794" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32169,7 +32169,7 @@
       </c>
       <c r="H795" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="H796" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32249,7 +32249,7 @@
       </c>
       <c r="H797" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32289,7 +32289,7 @@
       </c>
       <c r="H798" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32329,7 +32329,7 @@
       </c>
       <c r="H799" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32369,7 +32369,7 @@
       </c>
       <c r="H800" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32409,7 +32409,7 @@
       </c>
       <c r="H801" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32449,7 +32449,7 @@
       </c>
       <c r="H802" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="H803" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32529,7 +32529,7 @@
       </c>
       <c r="H804" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32569,7 +32569,7 @@
       </c>
       <c r="H805" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32609,7 +32609,7 @@
       </c>
       <c r="H806" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32649,7 +32649,7 @@
       </c>
       <c r="H807" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32689,7 +32689,7 @@
       </c>
       <c r="H808" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32729,7 +32729,7 @@
       </c>
       <c r="H809" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32769,7 +32769,7 @@
       </c>
       <c r="H810" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32809,7 +32809,7 @@
       </c>
       <c r="H811" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/price-list): Resolved URL: http://localhost:3001/finance/price-list</t>
         </is>
       </c>
     </row>
@@ -32849,7 +32849,7 @@
       </c>
       <c r="H812" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -32889,7 +32889,7 @@
       </c>
       <c r="H813" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -32929,7 +32929,7 @@
       </c>
       <c r="H814" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -32969,7 +32969,7 @@
       </c>
       <c r="H815" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="H816" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33049,7 +33049,7 @@
       </c>
       <c r="H817" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33089,7 +33089,7 @@
       </c>
       <c r="H818" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="H819" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33169,7 +33169,7 @@
       </c>
       <c r="H820" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33209,7 +33209,7 @@
       </c>
       <c r="H821" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33249,7 +33249,7 @@
       </c>
       <c r="H822" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33289,7 +33289,7 @@
       </c>
       <c r="H823" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33329,7 +33329,7 @@
       </c>
       <c r="H824" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33369,7 +33369,7 @@
       </c>
       <c r="H825" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33409,7 +33409,7 @@
       </c>
       <c r="H826" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33449,7 +33449,7 @@
       </c>
       <c r="H827" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33489,7 +33489,7 @@
       </c>
       <c r="H828" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33529,7 +33529,7 @@
       </c>
       <c r="H829" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33569,7 +33569,7 @@
       </c>
       <c r="H830" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33609,7 +33609,7 @@
       </c>
       <c r="H831" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33649,7 +33649,7 @@
       </c>
       <c r="H832" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33689,7 +33689,7 @@
       </c>
       <c r="H833" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="H834" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33769,7 +33769,7 @@
       </c>
       <c r="H835" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33809,7 +33809,7 @@
       </c>
       <c r="H836" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="H837" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33889,7 +33889,7 @@
       </c>
       <c r="H838" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="H839" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -33969,7 +33969,7 @@
       </c>
       <c r="H840" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34009,7 +34009,7 @@
       </c>
       <c r="H841" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="H842" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34089,7 +34089,7 @@
       </c>
       <c r="H843" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34129,7 +34129,7 @@
       </c>
       <c r="H844" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34169,7 +34169,7 @@
       </c>
       <c r="H845" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34209,7 +34209,7 @@
       </c>
       <c r="H846" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34249,7 +34249,7 @@
       </c>
       <c r="H847" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34289,7 +34289,7 @@
       </c>
       <c r="H848" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34329,7 +34329,7 @@
       </c>
       <c r="H849" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34369,7 +34369,7 @@
       </c>
       <c r="H850" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34409,7 +34409,7 @@
       </c>
       <c r="H851" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34449,7 +34449,7 @@
       </c>
       <c r="H852" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34489,7 +34489,7 @@
       </c>
       <c r="H853" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="H854" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34569,7 +34569,7 @@
       </c>
       <c r="H855" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34609,7 +34609,7 @@
       </c>
       <c r="H856" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34649,7 +34649,7 @@
       </c>
       <c r="H857" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34689,7 +34689,7 @@
       </c>
       <c r="H858" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34729,7 +34729,7 @@
       </c>
       <c r="H859" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34769,7 +34769,7 @@
       </c>
       <c r="H860" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34809,7 +34809,7 @@
       </c>
       <c r="H861" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34849,7 +34849,7 @@
       </c>
       <c r="H862" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34889,7 +34889,7 @@
       </c>
       <c r="H863" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34929,7 +34929,7 @@
       </c>
       <c r="H864" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="H865" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -35009,7 +35009,7 @@
       </c>
       <c r="H866" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="H867" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -35089,7 +35089,7 @@
       </c>
       <c r="H868" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -35129,7 +35129,7 @@
       </c>
       <c r="H869" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /finance/invoices): Resolved URL: http://localhost:3001/finance/invoices</t>
         </is>
       </c>
     </row>
@@ -35169,7 +35169,7 @@
       </c>
       <c r="H870" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35209,7 +35209,7 @@
       </c>
       <c r="H871" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35249,7 +35249,7 @@
       </c>
       <c r="H872" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="H873" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35329,7 +35329,7 @@
       </c>
       <c r="H874" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="H875" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35409,7 +35409,7 @@
       </c>
       <c r="H876" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35449,7 +35449,7 @@
       </c>
       <c r="H877" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35489,7 +35489,7 @@
       </c>
       <c r="H878" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35529,7 +35529,7 @@
       </c>
       <c r="H879" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35569,7 +35569,7 @@
       </c>
       <c r="H880" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35609,7 +35609,7 @@
       </c>
       <c r="H881" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35649,7 +35649,7 @@
       </c>
       <c r="H882" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35689,7 +35689,7 @@
       </c>
       <c r="H883" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35729,7 +35729,7 @@
       </c>
       <c r="H884" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35769,7 +35769,7 @@
       </c>
       <c r="H885" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35809,7 +35809,7 @@
       </c>
       <c r="H886" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35849,7 +35849,7 @@
       </c>
       <c r="H887" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35889,7 +35889,7 @@
       </c>
       <c r="H888" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35929,7 +35929,7 @@
       </c>
       <c r="H889" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -35969,7 +35969,7 @@
       </c>
       <c r="H890" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36009,7 +36009,7 @@
       </c>
       <c r="H891" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="H892" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36089,7 +36089,7 @@
       </c>
       <c r="H893" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36129,7 +36129,7 @@
       </c>
       <c r="H894" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36169,7 +36169,7 @@
       </c>
       <c r="H895" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36209,7 +36209,7 @@
       </c>
       <c r="H896" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36249,7 +36249,7 @@
       </c>
       <c r="H897" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36289,7 +36289,7 @@
       </c>
       <c r="H898" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36329,7 +36329,7 @@
       </c>
       <c r="H899" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36369,7 +36369,7 @@
       </c>
       <c r="H900" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36409,7 +36409,7 @@
       </c>
       <c r="H901" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="H902" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36489,7 +36489,7 @@
       </c>
       <c r="H903" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36529,7 +36529,7 @@
       </c>
       <c r="H904" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36569,7 +36569,7 @@
       </c>
       <c r="H905" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36609,7 +36609,7 @@
       </c>
       <c r="H906" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36649,7 +36649,7 @@
       </c>
       <c r="H907" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36689,7 +36689,7 @@
       </c>
       <c r="H908" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36729,7 +36729,7 @@
       </c>
       <c r="H909" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36769,7 +36769,7 @@
       </c>
       <c r="H910" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: Validated negative edge case correctly</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="H911" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36849,7 +36849,7 @@
       </c>
       <c r="H912" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36889,7 +36889,7 @@
       </c>
       <c r="H913" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36929,7 +36929,7 @@
       </c>
       <c r="H914" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -36969,7 +36969,7 @@
       </c>
       <c r="H915" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /inbound/returns): Resolved URL: http://localhost:3001/inbound/returns</t>
         </is>
       </c>
     </row>
@@ -37009,7 +37009,7 @@
       </c>
       <c r="H916" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37049,7 +37049,7 @@
       </c>
       <c r="H917" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37089,7 +37089,7 @@
       </c>
       <c r="H918" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37129,7 +37129,7 @@
       </c>
       <c r="H919" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37169,7 +37169,7 @@
       </c>
       <c r="H920" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37209,7 +37209,7 @@
       </c>
       <c r="H921" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37249,7 +37249,7 @@
       </c>
       <c r="H922" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37289,7 +37289,7 @@
       </c>
       <c r="H923" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37329,7 +37329,7 @@
       </c>
       <c r="H924" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37369,7 +37369,7 @@
       </c>
       <c r="H925" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37409,7 +37409,7 @@
       </c>
       <c r="H926" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37449,7 +37449,7 @@
       </c>
       <c r="H927" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37489,7 +37489,7 @@
       </c>
       <c r="H928" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>
@@ -37529,7 +37529,7 @@
       </c>
       <c r="H929" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E: UI component and workflow navigation verified</t>
+          <t>Selenium E2E module smoke check (CEO role, /reports/ceo-dashboard): Resolved URL: http://localhost:3001/reports/ceo-dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/test/selenium_error.xlsx
+++ b/docs/test/selenium_error.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24 23:11:39</t>
+          <t>2026-07-25 08:31:08</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
@@ -602,7 +602,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F159" s="7" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="H168" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="H170" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="H171" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F172" s="7" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="H172" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="H173" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F174" s="7" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="H174" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="H175" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="H178" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F194" s="7" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F197" s="7" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F202" s="7" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="H202" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F203" s="7" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E204" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F204" s="7" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="E206" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F207" s="7" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="E208" s="8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F208" s="7" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): ok</t>
+          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="H409" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="H410" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="H411" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="H412" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H413" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="H414" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="H415" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17017,7 +17017,7 @@
       </c>
       <c r="H416" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17057,7 +17057,7 @@
       </c>
       <c r="H417" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
       </c>
       <c r="H418" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17137,7 +17137,7 @@
       </c>
       <c r="H419" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="H420" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="H421" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17257,7 +17257,7 @@
       </c>
       <c r="H422" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="H423" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17337,7 @@
       </c>
       <c r="H424" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17377,7 +17377,7 @@
       </c>
       <c r="H425" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="H426" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="H427" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="H428" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17537,7 +17537,7 @@
       </c>
       <c r="H429" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="H430" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="H431" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="H432" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="H433" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="H434" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="H435" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17817,7 +17817,7 @@
       </c>
       <c r="H436" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17857,7 +17857,7 @@
       </c>
       <c r="H437" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17897,7 +17897,7 @@
       </c>
       <c r="H438" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17937,7 +17937,7 @@
       </c>
       <c r="H439" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17977,7 +17977,7 @@
       </c>
       <c r="H440" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="H441" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18057,7 +18057,7 @@
       </c>
       <c r="H442" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18097,7 +18097,7 @@
       </c>
       <c r="H443" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18137,7 +18137,7 @@
       </c>
       <c r="H444" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18177,7 +18177,7 @@
       </c>
       <c r="H445" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18217,7 +18217,7 @@
       </c>
       <c r="H446" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18257,7 +18257,7 @@
       </c>
       <c r="H447" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18297,7 +18297,7 @@
       </c>
       <c r="H448" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18337,7 +18337,7 @@
       </c>
       <c r="H449" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="H450" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18417,7 +18417,7 @@
       </c>
       <c r="H451" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="H452" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="H453" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="H454" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
       </c>
       <c r="H455" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18617,7 +18617,7 @@
       </c>
       <c r="H456" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="H457" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18697,7 +18697,7 @@
       </c>
       <c r="H458" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="H459" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="H460" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18817,7 +18817,7 @@
       </c>
       <c r="H461" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="H462" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18897,7 +18897,7 @@
       </c>
       <c r="H463" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="H464" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="H465" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="H466" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19057,7 +19057,7 @@
       </c>
       <c r="H467" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H468" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="H469" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
       </c>
       <c r="H470" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="H471" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="H472" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="H473" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H474" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19377,7 +19377,7 @@
       </c>
       <c r="H475" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="H476" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="H477" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19497,7 +19497,7 @@
       </c>
       <c r="H478" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="H479" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="H480" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="H481" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19657,7 +19657,7 @@
       </c>
       <c r="H482" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19697,7 +19697,7 @@
       </c>
       <c r="H483" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19737,7 +19737,7 @@
       </c>
       <c r="H484" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19777,7 +19777,7 @@
       </c>
       <c r="H485" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="H486" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19857,7 +19857,7 @@
       </c>
       <c r="H487" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="H488" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19937,7 +19937,7 @@
       </c>
       <c r="H489" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="H490" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="H491" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20057,7 +20057,7 @@
       </c>
       <c r="H492" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20097,7 +20097,7 @@
       </c>
       <c r="H493" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="H494" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="H495" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20217,7 +20217,7 @@
       </c>
       <c r="H496" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20257,7 +20257,7 @@
       </c>
       <c r="H497" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20297,7 +20297,7 @@
       </c>
       <c r="H498" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="H499" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="H500" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20417,7 +20417,7 @@
       </c>
       <c r="H501" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20457,7 +20457,7 @@
       </c>
       <c r="H502" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20497,7 +20497,7 @@
       </c>
       <c r="H503" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20537,7 +20537,7 @@
       </c>
       <c r="H504" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="H505" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20617,7 +20617,7 @@
       </c>
       <c r="H506" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="H507" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="H508" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20737,7 +20737,7 @@
       </c>
       <c r="H509" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20777,7 +20777,7 @@
       </c>
       <c r="H510" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20817,7 +20817,7 @@
       </c>
       <c r="H511" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20857,7 +20857,7 @@
       </c>
       <c r="H512" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="H513" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="H514" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20977,7 +20977,7 @@
       </c>
       <c r="H515" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21017,7 +21017,7 @@
       </c>
       <c r="H516" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21057,7 +21057,7 @@
       </c>
       <c r="H517" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21097,7 +21097,7 @@
       </c>
       <c r="H518" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="H519" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21177,7 +21177,7 @@
       </c>
       <c r="H520" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="H521" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="H522" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21297,7 +21297,7 @@
       </c>
       <c r="H523" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="H524" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="H525" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="H526" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after two send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="H527" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21497,7 +21497,7 @@
       </c>
       <c r="H528" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21537,7 +21537,7 @@
       </c>
       <c r="H529" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21577,7 +21577,7 @@
       </c>
       <c r="H530" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="H531" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21657,7 +21657,7 @@
       </c>
       <c r="H532" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21697,7 +21697,7 @@
       </c>
       <c r="H533" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21737,7 +21737,7 @@
       </c>
       <c r="H534" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H535" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21817,7 +21817,7 @@
       </c>
       <c r="H536" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21857,7 +21857,7 @@
       </c>
       <c r="H537" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21897,7 +21897,7 @@
       </c>
       <c r="H538" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21937,7 +21937,7 @@
       </c>
       <c r="H539" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
       </c>
       <c r="H540" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22017,7 +22017,7 @@
       </c>
       <c r="H541" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22057,7 +22057,7 @@
       </c>
       <c r="H542" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22097,7 +22097,7 @@
       </c>
       <c r="H543" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22137,7 +22137,7 @@
       </c>
       <c r="H544" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="H545" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22217,7 +22217,7 @@
       </c>
       <c r="H546" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22257,7 +22257,7 @@
       </c>
       <c r="H547" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22297,7 +22297,7 @@
       </c>
       <c r="H548" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22337,7 +22337,7 @@
       </c>
       <c r="H549" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22377,7 +22377,7 @@
       </c>
       <c r="H550" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22417,7 +22417,7 @@
       </c>
       <c r="H551" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="H552" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22497,7 +22497,7 @@
       </c>
       <c r="H553" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="H554" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22577,7 +22577,7 @@
       </c>
       <c r="H555" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22617,7 +22617,7 @@
       </c>
       <c r="H556" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22657,7 +22657,7 @@
       </c>
       <c r="H557" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22697,7 +22697,7 @@
       </c>
       <c r="H558" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22737,7 +22737,7 @@
       </c>
       <c r="H559" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22777,7 +22777,7 @@
       </c>
       <c r="H560" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="H561" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="H562" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="H563" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="H564" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22977,7 +22977,7 @@
       </c>
       <c r="H565" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="H566" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="H567" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="H568" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23137,7 +23137,7 @@
       </c>
       <c r="H569" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23177,7 +23177,7 @@
       </c>
       <c r="H570" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23217,7 +23217,7 @@
       </c>
       <c r="H571" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23257,7 +23257,7 @@
       </c>
       <c r="H572" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23297,7 +23297,7 @@
       </c>
       <c r="H573" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23337,7 +23337,7 @@
       </c>
       <c r="H574" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23377,7 +23377,7 @@
       </c>
       <c r="H575" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23417,7 +23417,7 @@
       </c>
       <c r="H576" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="H577" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23497,7 +23497,7 @@
       </c>
       <c r="H578" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23537,7 +23537,7 @@
       </c>
       <c r="H579" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23577,7 +23577,7 @@
       </c>
       <c r="H580" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23617,7 +23617,7 @@
       </c>
       <c r="H581" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23657,7 +23657,7 @@
       </c>
       <c r="H582" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="H583" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23737,7 +23737,7 @@
       </c>
       <c r="H584" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="H585" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23817,7 +23817,7 @@
       </c>
       <c r="H586" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23857,7 +23857,7 @@
       </c>
       <c r="H587" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23897,7 +23897,7 @@
       </c>
       <c r="H588" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="H589" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23977,7 +23977,7 @@
       </c>
       <c r="H590" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="H591" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24057,7 +24057,7 @@
       </c>
       <c r="H592" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24097,7 +24097,7 @@
       </c>
       <c r="H593" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24137,7 +24137,7 @@
       </c>
       <c r="H594" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24177,7 +24177,7 @@
       </c>
       <c r="H595" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H596" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24257,7 +24257,7 @@
       </c>
       <c r="H597" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24297,7 +24297,7 @@
       </c>
       <c r="H598" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24337,7 +24337,7 @@
       </c>
       <c r="H599" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24377,7 +24377,7 @@
       </c>
       <c r="H600" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="H601" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="H602" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="H603" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="H604" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="H605" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24617,7 +24617,7 @@
       </c>
       <c r="H606" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24657,7 +24657,7 @@
       </c>
       <c r="H607" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24697,7 +24697,7 @@
       </c>
       <c r="H608" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24737,7 +24737,7 @@
       </c>
       <c r="H609" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24777,7 +24777,7 @@
       </c>
       <c r="H610" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24817,7 +24817,7 @@
       </c>
       <c r="H611" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="H612" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24897,7 +24897,7 @@
       </c>
       <c r="H613" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24937,7 +24937,7 @@
       </c>
       <c r="H614" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24977,7 +24977,7 @@
       </c>
       <c r="H615" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25017,7 +25017,7 @@
       </c>
       <c r="H616" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25057,7 +25057,7 @@
       </c>
       <c r="H617" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25097,7 +25097,7 @@
       </c>
       <c r="H618" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="H619" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25177,7 +25177,7 @@
       </c>
       <c r="H620" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="H621" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="H622" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25297,7 +25297,7 @@
       </c>
       <c r="H623" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25337,7 +25337,7 @@
       </c>
       <c r="H624" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25377,7 +25377,7 @@
       </c>
       <c r="H625" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25417,7 +25417,7 @@
       </c>
       <c r="H626" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25457,7 +25457,7 @@
       </c>
       <c r="H627" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="H628" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25537,7 +25537,7 @@
       </c>
       <c r="H629" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="H630" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25617,7 +25617,7 @@
       </c>
       <c r="H631" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25657,7 +25657,7 @@
       </c>
       <c r="H632" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25697,7 +25697,7 @@
       </c>
       <c r="H633" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25737,7 +25737,7 @@
       </c>
       <c r="H634" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25777,7 +25777,7 @@
       </c>
       <c r="H635" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25817,7 +25817,7 @@
       </c>
       <c r="H636" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25857,7 +25857,7 @@
       </c>
       <c r="H637" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25897,7 +25897,7 @@
       </c>
       <c r="H638" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="H639" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="H640" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26017,7 +26017,7 @@
       </c>
       <c r="H641" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="H642" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26097,7 +26097,7 @@
       </c>
       <c r="H643" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="H644" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26177,7 +26177,7 @@
       </c>
       <c r="H645" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26217,7 +26217,7 @@
       </c>
       <c r="H646" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26257,7 +26257,7 @@
       </c>
       <c r="H647" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26297,7 +26297,7 @@
       </c>
       <c r="H648" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26337,7 +26337,7 @@
       </c>
       <c r="H649" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26377,7 +26377,7 @@
       </c>
       <c r="H650" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26417,7 +26417,7 @@
       </c>
       <c r="H651" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26457,7 +26457,7 @@
       </c>
       <c r="H652" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26497,7 +26497,7 @@
       </c>
       <c r="H653" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26537,7 +26537,7 @@
       </c>
       <c r="H654" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26577,7 +26577,7 @@
       </c>
       <c r="H655" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26617,7 +26617,7 @@
       </c>
       <c r="H656" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H657" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26697,7 +26697,7 @@
       </c>
       <c r="H658" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26737,7 +26737,7 @@
       </c>
       <c r="H659" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Exception: TimeoutException: Message: No element found for css selector='[data-testid='do-dealer-select']' within 10s (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -32082,7 +32082,7 @@
       </c>
       <c r="E793" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F793" s="7" t="inlineStr">
@@ -32097,7 +32097,7 @@
       </c>
       <c r="H793" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32122,7 +32122,7 @@
       </c>
       <c r="E794" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F794" s="7" t="inlineStr">
@@ -32137,7 +32137,7 @@
       </c>
       <c r="H794" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32162,7 +32162,7 @@
       </c>
       <c r="E795" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F795" s="7" t="inlineStr">
@@ -32177,7 +32177,7 @@
       </c>
       <c r="H795" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32202,7 +32202,7 @@
       </c>
       <c r="E796" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F796" s="7" t="inlineStr">
@@ -32217,7 +32217,7 @@
       </c>
       <c r="H796" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32242,7 +32242,7 @@
       </c>
       <c r="E797" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F797" s="7" t="inlineStr">
@@ -32257,7 +32257,7 @@
       </c>
       <c r="H797" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32282,7 +32282,7 @@
       </c>
       <c r="E798" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F798" s="7" t="inlineStr">
@@ -32297,7 +32297,7 @@
       </c>
       <c r="H798" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32322,7 +32322,7 @@
       </c>
       <c r="E799" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F799" s="7" t="inlineStr">
@@ -32337,7 +32337,7 @@
       </c>
       <c r="H799" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32362,7 +32362,7 @@
       </c>
       <c r="E800" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F800" s="7" t="inlineStr">
@@ -32377,7 +32377,7 @@
       </c>
       <c r="H800" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32402,7 +32402,7 @@
       </c>
       <c r="E801" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F801" s="7" t="inlineStr">
@@ -32417,7 +32417,7 @@
       </c>
       <c r="H801" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32442,7 +32442,7 @@
       </c>
       <c r="E802" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F802" s="7" t="inlineStr">
@@ -32457,7 +32457,7 @@
       </c>
       <c r="H802" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32482,7 +32482,7 @@
       </c>
       <c r="E803" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F803" s="7" t="inlineStr">
@@ -32497,7 +32497,7 @@
       </c>
       <c r="H803" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32522,7 +32522,7 @@
       </c>
       <c r="E804" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F804" s="7" t="inlineStr">
@@ -32537,7 +32537,7 @@
       </c>
       <c r="H804" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32562,7 +32562,7 @@
       </c>
       <c r="E805" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F805" s="7" t="inlineStr">
@@ -32577,7 +32577,7 @@
       </c>
       <c r="H805" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32602,7 +32602,7 @@
       </c>
       <c r="E806" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F806" s="7" t="inlineStr">
@@ -32617,7 +32617,7 @@
       </c>
       <c r="H806" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32642,7 +32642,7 @@
       </c>
       <c r="E807" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F807" s="7" t="inlineStr">
@@ -32657,7 +32657,7 @@
       </c>
       <c r="H807" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="E808" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F808" s="7" t="inlineStr">
@@ -32697,7 +32697,7 @@
       </c>
       <c r="H808" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="E809" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F809" s="7" t="inlineStr">
@@ -32737,7 +32737,7 @@
       </c>
       <c r="H809" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32762,7 +32762,7 @@
       </c>
       <c r="E810" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F810" s="7" t="inlineStr">
@@ -32777,7 +32777,7 @@
       </c>
       <c r="H810" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32802,7 +32802,7 @@
       </c>
       <c r="E811" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F811" s="7" t="inlineStr">
@@ -32817,7 +32817,7 @@
       </c>
       <c r="H811" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): No product matched search term 'a' (input actually held 'a'; dropdown rendered but showed no results) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: PRC-007-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32857,7 +32857,7 @@
       </c>
       <c r="H812" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -32897,7 +32897,7 @@
       </c>
       <c r="H813" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -32937,7 +32937,7 @@
       </c>
       <c r="H814" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -32977,7 +32977,7 @@
       </c>
       <c r="H815" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33017,7 +33017,7 @@
       </c>
       <c r="H816" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33057,7 +33057,7 @@
       </c>
       <c r="H817" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="H818" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33137,7 +33137,7 @@
       </c>
       <c r="H819" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33177,7 +33177,7 @@
       </c>
       <c r="H820" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33217,7 +33217,7 @@
       </c>
       <c r="H821" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33257,7 +33257,7 @@
       </c>
       <c r="H822" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33297,7 +33297,7 @@
       </c>
       <c r="H823" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33337,7 +33337,7 @@
       </c>
       <c r="H824" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33377,7 +33377,7 @@
       </c>
       <c r="H825" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33417,7 +33417,7 @@
       </c>
       <c r="H826" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33457,7 +33457,7 @@
       </c>
       <c r="H827" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="H828" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33537,7 +33537,7 @@
       </c>
       <c r="H829" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33577,7 +33577,7 @@
       </c>
       <c r="H830" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33617,7 +33617,7 @@
       </c>
       <c r="H831" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33657,7 +33657,7 @@
       </c>
       <c r="H832" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33697,7 +33697,7 @@
       </c>
       <c r="H833" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33737,7 +33737,7 @@
       </c>
       <c r="H834" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33777,7 +33777,7 @@
       </c>
       <c r="H835" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33817,7 +33817,7 @@
       </c>
       <c r="H836" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33857,7 +33857,7 @@
       </c>
       <c r="H837" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="H838" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33937,7 +33937,7 @@
       </c>
       <c r="H839" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H840" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34017,7 +34017,7 @@
       </c>
       <c r="H841" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34057,7 +34057,7 @@
       </c>
       <c r="H842" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34097,7 +34097,7 @@
       </c>
       <c r="H843" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34137,7 +34137,7 @@
       </c>
       <c r="H844" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34177,7 +34177,7 @@
       </c>
       <c r="H845" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34217,7 +34217,7 @@
       </c>
       <c r="H846" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34257,7 +34257,7 @@
       </c>
       <c r="H847" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34297,7 +34297,7 @@
       </c>
       <c r="H848" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34337,7 +34337,7 @@
       </c>
       <c r="H849" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34377,7 +34377,7 @@
       </c>
       <c r="H850" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="H851" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34457,7 +34457,7 @@
       </c>
       <c r="H852" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34497,7 +34497,7 @@
       </c>
       <c r="H853" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34537,7 +34537,7 @@
       </c>
       <c r="H854" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34577,7 +34577,7 @@
       </c>
       <c r="H855" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34617,7 +34617,7 @@
       </c>
       <c r="H856" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="H857" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34697,7 +34697,7 @@
       </c>
       <c r="H858" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34737,7 +34737,7 @@
       </c>
       <c r="H859" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34777,7 +34777,7 @@
       </c>
       <c r="H860" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34817,7 +34817,7 @@
       </c>
       <c r="H861" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34857,7 +34857,7 @@
       </c>
       <c r="H862" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34897,7 +34897,7 @@
       </c>
       <c r="H863" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34937,7 +34937,7 @@
       </c>
       <c r="H864" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -34977,7 +34977,7 @@
       </c>
       <c r="H865" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35017,7 +35017,7 @@
       </c>
       <c r="H866" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35057,7 +35057,7 @@
       </c>
       <c r="H867" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35097,7 +35097,7 @@
       </c>
       <c r="H868" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35137,7 +35137,7 @@
       </c>
       <c r="H869" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): Skipped: no unpaid invoice available for the default dealer to test payment recording against | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: FIN-008-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35160,9 +35160,9 @@
           <t>Create Disposal Success</t>
         </is>
       </c>
-      <c r="E870" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E870" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F870" s="7" t="inlineStr">
@@ -35177,7 +35177,7 @@
       </c>
       <c r="H870" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35200,9 +35200,9 @@
           <t>Get Pending Disposals Success</t>
         </is>
       </c>
-      <c r="E871" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E871" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F871" s="7" t="inlineStr">
@@ -35217,7 +35217,7 @@
       </c>
       <c r="H871" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35240,9 +35240,9 @@
           <t>Approve Disposal Success</t>
         </is>
       </c>
-      <c r="E872" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E872" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F872" s="7" t="inlineStr">
@@ -35257,7 +35257,7 @@
       </c>
       <c r="H872" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35280,9 +35280,9 @@
           <t>Create Return Receipt Success</t>
         </is>
       </c>
-      <c r="E873" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E873" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F873" s="7" t="inlineStr">
@@ -35297,7 +35297,7 @@
       </c>
       <c r="H873" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35320,9 +35320,9 @@
           <t>Process Return Qc Success</t>
         </is>
       </c>
-      <c r="E874" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E874" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F874" s="7" t="inlineStr">
@@ -35337,7 +35337,7 @@
       </c>
       <c r="H874" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35360,9 +35360,9 @@
           <t>Create Credit Note Success</t>
         </is>
       </c>
-      <c r="E875" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E875" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F875" s="7" t="inlineStr">
@@ -35377,7 +35377,7 @@
       </c>
       <c r="H875" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35400,9 +35400,9 @@
           <t>Create Disposal Request Auto Approved Success</t>
         </is>
       </c>
-      <c r="E876" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E876" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F876" s="7" t="inlineStr">
@@ -35417,7 +35417,7 @@
       </c>
       <c r="H876" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35440,9 +35440,9 @@
           <t>Create Disposal Request Requires Approval Success</t>
         </is>
       </c>
-      <c r="E877" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E877" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F877" s="7" t="inlineStr">
@@ -35457,7 +35457,7 @@
       </c>
       <c r="H877" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35480,9 +35480,9 @@
           <t>Approve Disposal Manager Success</t>
         </is>
       </c>
-      <c r="E878" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E878" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F878" s="7" t="inlineStr">
@@ -35497,7 +35497,7 @@
       </c>
       <c r="H878" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35520,9 +35520,9 @@
           <t>Approve Disposal High Value Requires Ceo Fails For Manager</t>
         </is>
       </c>
-      <c r="E879" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E879" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F879" s="7" t="inlineStr">
@@ -35537,7 +35537,7 @@
       </c>
       <c r="H879" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35560,9 +35560,9 @@
           <t>Create Disposal Request Return Receipt Approved Success</t>
         </is>
       </c>
-      <c r="E880" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E880" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F880" s="7" t="inlineStr">
@@ -35577,7 +35577,7 @@
       </c>
       <c r="H880" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35600,9 +35600,9 @@
           <t>Create Disposal From Quarantine Success</t>
         </is>
       </c>
-      <c r="E881" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E881" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F881" s="7" t="inlineStr">
@@ -35617,7 +35617,7 @@
       </c>
       <c r="H881" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35640,9 +35640,9 @@
           <t>Approve Disposal Quarantine Record Success</t>
         </is>
       </c>
-      <c r="E882" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E882" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F882" s="7" t="inlineStr">
@@ -35657,7 +35657,7 @@
       </c>
       <c r="H882" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35680,9 +35680,9 @@
           <t>Confirm Rtv Full Quantity Deducts Quarantine Inventory</t>
         </is>
       </c>
-      <c r="E883" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E883" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F883" s="7" t="inlineStr">
@@ -35697,7 +35697,7 @@
       </c>
       <c r="H883" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35720,9 +35720,9 @@
           <t>Confirm Rtv Happy Path Audit Log Contains Deducted Qty</t>
         </is>
       </c>
-      <c r="E884" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E884" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F884" s="7" t="inlineStr">
@@ -35737,7 +35737,7 @@
       </c>
       <c r="H884" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35760,9 +35760,9 @@
           <t>Confirm Rtv Partial Quantity Throws Business Rule Violation</t>
         </is>
       </c>
-      <c r="E885" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E885" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F885" s="7" t="inlineStr">
@@ -35777,7 +35777,7 @@
       </c>
       <c r="H885" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35800,9 +35800,9 @@
           <t>Confirm Rtv More Quantity Than Quarantine Throws Business Rule Violation</t>
         </is>
       </c>
-      <c r="E886" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E886" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F886" s="7" t="inlineStr">
@@ -35817,7 +35817,7 @@
       </c>
       <c r="H886" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35840,9 +35840,9 @@
           <t>Confirm Rtv Already Confirmed Throws Business Rule Violation</t>
         </is>
       </c>
-      <c r="E887" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E887" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F887" s="7" t="inlineStr">
@@ -35857,7 +35857,7 @@
       </c>
       <c r="H887" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35880,9 +35880,9 @@
           <t>Confirm Rtv Deduction Would Result In Negative Inventory Throws Business Rule Violation</t>
         </is>
       </c>
-      <c r="E888" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E888" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F888" s="7" t="inlineStr">
@@ -35897,7 +35897,7 @@
       </c>
       <c r="H888" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35920,9 +35920,9 @@
           <t>Confirm Rtv Receipt Status Remains Qc Failed</t>
         </is>
       </c>
-      <c r="E889" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E889" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F889" s="7" t="inlineStr">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="H889" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35960,9 +35960,9 @@
           <t>Create Rtv Happy Path Creates Pending Adjustment And Debit Note</t>
         </is>
       </c>
-      <c r="E890" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E890" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F890" s="7" t="inlineStr">
@@ -35977,7 +35977,7 @@
       </c>
       <c r="H890" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36000,9 +36000,9 @@
           <t>Create Rtv Happy Path Does Not Deduct Quarantine Inventory</t>
         </is>
       </c>
-      <c r="E891" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E891" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F891" s="7" t="inlineStr">
@@ -36017,7 +36017,7 @@
       </c>
       <c r="H891" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36040,9 +36040,9 @@
           <t>Create Rtv Happy Path Audit Log Contains Inventory Deducted False</t>
         </is>
       </c>
-      <c r="E892" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E892" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F892" s="7" t="inlineStr">
@@ -36057,7 +36057,7 @@
       </c>
       <c r="H892" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36080,9 +36080,9 @@
           <t>Create Rtv Duplicate Rtv Throws Rtv Already Exists</t>
         </is>
       </c>
-      <c r="E893" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E893" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F893" s="7" t="inlineStr">
@@ -36097,7 +36097,7 @@
       </c>
       <c r="H893" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36120,9 +36120,9 @@
           <t>Create Rtv Approved Status Throws Business Rule Violation</t>
         </is>
       </c>
-      <c r="E894" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E894" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F894" s="7" t="inlineStr">
@@ -36137,7 +36137,7 @@
       </c>
       <c r="H894" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36160,9 +36160,9 @@
           <t>Create Rtv Qc Completed Status Throws Business Rule Violation</t>
         </is>
       </c>
-      <c r="E895" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E895" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F895" s="7" t="inlineStr">
@@ -36177,7 +36177,7 @@
       </c>
       <c r="H895" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36200,9 +36200,9 @@
           <t>Create Rtv No Items Throws Business Rule Violation</t>
         </is>
       </c>
-      <c r="E896" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E896" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F896" s="7" t="inlineStr">
@@ -36217,7 +36217,7 @@
       </c>
       <c r="H896" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36240,9 +36240,9 @@
           <t>Create Rtv Forbidden Warehouse Throws Forbidden Receipt Warehouse</t>
         </is>
       </c>
-      <c r="E897" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E897" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F897" s="7" t="inlineStr">
@@ -36257,7 +36257,7 @@
       </c>
       <c r="H897" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36280,9 +36280,9 @@
           <t>Create Rtv Return Receipt Approved Creates Pending Adjustment And Debit Note</t>
         </is>
       </c>
-      <c r="E898" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E898" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F898" s="7" t="inlineStr">
@@ -36297,7 +36297,7 @@
       </c>
       <c r="H898" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36320,9 +36320,9 @@
           <t>Reject Receipt Happy Path Status Becomes Return Pending</t>
         </is>
       </c>
-      <c r="E899" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E899" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F899" s="7" t="inlineStr">
@@ -36337,7 +36337,7 @@
       </c>
       <c r="H899" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36360,9 +36360,9 @@
           <t>Reject Receipt Happy Path Does Not Create Batch Or Inventory Or Rtv</t>
         </is>
       </c>
-      <c r="E900" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E900" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F900" s="7" t="inlineStr">
@@ -36377,7 +36377,7 @@
       </c>
       <c r="H900" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36400,9 +36400,9 @@
           <t>Reject Receipt Missing Reason Throws Illegal Argument</t>
         </is>
       </c>
-      <c r="E901" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E901" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F901" s="7" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="H901" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36440,9 +36440,9 @@
           <t>Reject Receipt Blank Reason Throws Illegal Argument</t>
         </is>
       </c>
-      <c r="E902" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E902" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F902" s="7" t="inlineStr">
@@ -36457,7 +36457,7 @@
       </c>
       <c r="H902" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36480,9 +36480,9 @@
           <t>Reject Receipt Already Approved Throws Receipt Already Decided</t>
         </is>
       </c>
-      <c r="E903" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E903" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F903" s="7" t="inlineStr">
@@ -36497,7 +36497,7 @@
       </c>
       <c r="H903" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36520,9 +36520,9 @@
           <t>Reject Receipt Qc Failed Throws Business Rule Violation</t>
         </is>
       </c>
-      <c r="E904" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E904" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F904" s="7" t="inlineStr">
@@ -36537,7 +36537,7 @@
       </c>
       <c r="H904" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36560,9 +36560,9 @@
           <t>Confirm Return To Supplier Happy Path Status Becomes Returned To Supplier</t>
         </is>
       </c>
-      <c r="E905" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E905" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F905" s="7" t="inlineStr">
@@ -36577,7 +36577,7 @@
       </c>
       <c r="H905" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36600,9 +36600,9 @@
           <t>Confirm Return To Supplier Happy Path Does Not Create Inventory Or Rtv</t>
         </is>
       </c>
-      <c r="E906" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E906" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F906" s="7" t="inlineStr">
@@ -36617,7 +36617,7 @@
       </c>
       <c r="H906" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36640,9 +36640,9 @@
           <t>Confirm Return To Supplier Wrong State Approved Throws Business Rule Violation</t>
         </is>
       </c>
-      <c r="E907" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E907" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F907" s="7" t="inlineStr">
@@ -36657,7 +36657,7 @@
       </c>
       <c r="H907" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36680,9 +36680,9 @@
           <t>Confirm Return To Supplier Stale Version Throws Business Rule Violation</t>
         </is>
       </c>
-      <c r="E908" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E908" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F908" s="7" t="inlineStr">
@@ -36697,7 +36697,7 @@
       </c>
       <c r="H908" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36720,9 +36720,9 @@
           <t>Create Return Receipt Success</t>
         </is>
       </c>
-      <c r="E909" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E909" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F909" s="7" t="inlineStr">
@@ -36737,7 +36737,7 @@
       </c>
       <c r="H909" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36760,9 +36760,9 @@
           <t>Create Return Receipt Exceeds Original Sale Fails</t>
         </is>
       </c>
-      <c r="E910" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E910" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F910" s="7" t="inlineStr">
@@ -36777,7 +36777,7 @@
       </c>
       <c r="H910" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36800,9 +36800,9 @@
           <t>Process Return Qc Success</t>
         </is>
       </c>
-      <c r="E911" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E911" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F911" s="7" t="inlineStr">
@@ -36817,7 +36817,7 @@
       </c>
       <c r="H911" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36840,9 +36840,9 @@
           <t>Create Credit Note Success</t>
         </is>
       </c>
-      <c r="E912" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E912" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F912" s="7" t="inlineStr">
@@ -36857,7 +36857,7 @@
       </c>
       <c r="H912" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36880,9 +36880,9 @@
           <t>creates customer return receipt</t>
         </is>
       </c>
-      <c r="E913" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E913" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F913" s="7" t="inlineStr">
@@ -36897,7 +36897,7 @@
       </c>
       <c r="H913" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36920,9 +36920,9 @@
           <t>processes return QC items</t>
         </is>
       </c>
-      <c r="E914" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E914" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F914" s="7" t="inlineStr">
@@ -36937,7 +36937,7 @@
       </c>
       <c r="H914" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36960,9 +36960,9 @@
           <t>creates credit note for approved return</t>
         </is>
       </c>
-      <c r="E915" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E915" s="9" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="F915" s="7" t="inlineStr">
@@ -36977,7 +36977,7 @@
       </c>
       <c r="H915" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Skipped: no DELIVERED/COMPLETED delivery order available to build a return against (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit | Console errors: http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>

--- a/docs/test/selenium_error.xlsx
+++ b/docs/test/selenium_error.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25 08:31:08</t>
+          <t>2026-07-25 10:48:13</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F159" s="7" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="H168" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="H170" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="H171" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F172" s="7" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="H172" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="H173" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F174" s="7" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="H174" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="H175" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="H178" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F194" s="7" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F197" s="7" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F202" s="7" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="H202" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F203" s="7" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E204" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F204" s="7" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="E206" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F207" s="7" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="E208" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F208" s="7" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ADMIN role): Form/modal still open after submit (no error text found -- check screenshot) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: AUTH-001-round3.png)</t>
+          <t>Selenium E2E real business flow (ADMIN role): ok</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="H409" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="H410" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="H411" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="H412" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H413" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="H414" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="H415" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17017,7 +17017,7 @@
       </c>
       <c r="H416" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17057,7 +17057,7 @@
       </c>
       <c r="H417" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
       </c>
       <c r="H418" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17137,7 +17137,7 @@
       </c>
       <c r="H419" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="H420" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="H421" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17257,7 +17257,7 @@
       </c>
       <c r="H422" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="H423" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17337,7 @@
       </c>
       <c r="H424" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17377,7 +17377,7 @@
       </c>
       <c r="H425" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="H426" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="H427" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="H428" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17537,7 +17537,7 @@
       </c>
       <c r="H429" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="H430" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="H431" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="H432" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="H433" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="H434" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="H435" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17817,7 +17817,7 @@
       </c>
       <c r="H436" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17857,7 +17857,7 @@
       </c>
       <c r="H437" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17897,7 +17897,7 @@
       </c>
       <c r="H438" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17937,7 +17937,7 @@
       </c>
       <c r="H439" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -17977,7 +17977,7 @@
       </c>
       <c r="H440" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="H441" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18057,7 +18057,7 @@
       </c>
       <c r="H442" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18097,7 +18097,7 @@
       </c>
       <c r="H443" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18137,7 +18137,7 @@
       </c>
       <c r="H444" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18177,7 +18177,7 @@
       </c>
       <c r="H445" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18217,7 +18217,7 @@
       </c>
       <c r="H446" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18257,7 +18257,7 @@
       </c>
       <c r="H447" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18297,7 +18297,7 @@
       </c>
       <c r="H448" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18337,7 +18337,7 @@
       </c>
       <c r="H449" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="H450" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18417,7 +18417,7 @@
       </c>
       <c r="H451" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="H452" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="H453" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="H454" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
       </c>
       <c r="H455" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18617,7 +18617,7 @@
       </c>
       <c r="H456" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="H457" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18697,7 +18697,7 @@
       </c>
       <c r="H458" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="H459" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="H460" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18817,7 +18817,7 @@
       </c>
       <c r="H461" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="H462" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18897,7 +18897,7 @@
       </c>
       <c r="H463" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="H464" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="H465" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="H466" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19057,7 +19057,7 @@
       </c>
       <c r="H467" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H468" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="H469" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
       </c>
       <c r="H470" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="H471" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="H472" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="H473" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H474" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19377,7 +19377,7 @@
       </c>
       <c r="H475" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="H476" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="H477" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19497,7 +19497,7 @@
       </c>
       <c r="H478" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="H479" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="H480" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="H481" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19657,7 +19657,7 @@
       </c>
       <c r="H482" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19697,7 +19697,7 @@
       </c>
       <c r="H483" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19737,7 +19737,7 @@
       </c>
       <c r="H484" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19777,7 +19777,7 @@
       </c>
       <c r="H485" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="H486" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19857,7 +19857,7 @@
       </c>
       <c r="H487" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="H488" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19937,7 +19937,7 @@
       </c>
       <c r="H489" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="H490" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="H491" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20057,7 +20057,7 @@
       </c>
       <c r="H492" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20097,7 +20097,7 @@
       </c>
       <c r="H493" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="H494" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="H495" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20217,7 +20217,7 @@
       </c>
       <c r="H496" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20257,7 +20257,7 @@
       </c>
       <c r="H497" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20297,7 +20297,7 @@
       </c>
       <c r="H498" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="H499" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="H500" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20417,7 +20417,7 @@
       </c>
       <c r="H501" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20457,7 +20457,7 @@
       </c>
       <c r="H502" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20497,7 +20497,7 @@
       </c>
       <c r="H503" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20537,7 +20537,7 @@
       </c>
       <c r="H504" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="H505" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20617,7 +20617,7 @@
       </c>
       <c r="H506" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="H507" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="H508" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20737,7 +20737,7 @@
       </c>
       <c r="H509" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20777,7 +20777,7 @@
       </c>
       <c r="H510" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20817,7 +20817,7 @@
       </c>
       <c r="H511" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20857,7 +20857,7 @@
       </c>
       <c r="H512" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="H513" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="H514" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -20977,7 +20977,7 @@
       </c>
       <c r="H515" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21017,7 +21017,7 @@
       </c>
       <c r="H516" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21057,7 +21057,7 @@
       </c>
       <c r="H517" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21097,7 +21097,7 @@
       </c>
       <c r="H518" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="H519" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21177,7 +21177,7 @@
       </c>
       <c r="H520" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="H521" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="H522" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21297,7 +21297,7 @@
       </c>
       <c r="H523" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="H524" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="H525" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="H526" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Search input still shows '' after 3 send_keys attempts (expected 'a') | GET /products -&gt; status=200, body[:300]={"content":[{"id":70,"sku":"ASS","name":"a","unit":"Thùng","unitPerPack":1,"description":"","imageUrl":null,"weightKg":0.002,"volumeM3":0.00002,"reorderPoint":10.00,"isActive":true,"createdAt":"2026-07-12T11:20:02.467335Z","updatedAt":"2026-07-12T11:20:02.467335Z"},{"id":68,"sku":"SKU-111","name":"á | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Field for label 'Người liên hệ' still shows '' after two send_keys attempts (expected 'Selenium AutoTest'); document.activeElement was INPUT value="" | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: RCV-003-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="H527" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21497,7 +21497,7 @@
       </c>
       <c r="H528" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21537,7 +21537,7 @@
       </c>
       <c r="H529" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21577,7 +21577,7 @@
       </c>
       <c r="H530" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="H531" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21657,7 +21657,7 @@
       </c>
       <c r="H532" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21697,7 +21697,7 @@
       </c>
       <c r="H533" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21737,7 +21737,7 @@
       </c>
       <c r="H534" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H535" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21817,7 +21817,7 @@
       </c>
       <c r="H536" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21857,7 +21857,7 @@
       </c>
       <c r="H537" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21897,7 +21897,7 @@
       </c>
       <c r="H538" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21937,7 +21937,7 @@
       </c>
       <c r="H539" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
       </c>
       <c r="H540" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22017,7 +22017,7 @@
       </c>
       <c r="H541" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22057,7 +22057,7 @@
       </c>
       <c r="H542" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22097,7 +22097,7 @@
       </c>
       <c r="H543" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22137,7 +22137,7 @@
       </c>
       <c r="H544" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="H545" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22217,7 +22217,7 @@
       </c>
       <c r="H546" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22257,7 +22257,7 @@
       </c>
       <c r="H547" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22297,7 +22297,7 @@
       </c>
       <c r="H548" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22337,7 +22337,7 @@
       </c>
       <c r="H549" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22377,7 +22377,7 @@
       </c>
       <c r="H550" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22417,7 +22417,7 @@
       </c>
       <c r="H551" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="H552" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22497,7 +22497,7 @@
       </c>
       <c r="H553" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="H554" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22577,7 +22577,7 @@
       </c>
       <c r="H555" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22617,7 +22617,7 @@
       </c>
       <c r="H556" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22657,7 +22657,7 @@
       </c>
       <c r="H557" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22697,7 +22697,7 @@
       </c>
       <c r="H558" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22737,7 +22737,7 @@
       </c>
       <c r="H559" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22777,7 +22777,7 @@
       </c>
       <c r="H560" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="H561" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="H562" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="H563" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="H564" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -22977,7 +22977,7 @@
       </c>
       <c r="H565" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="H566" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="H567" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="H568" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23137,7 +23137,7 @@
       </c>
       <c r="H569" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23177,7 +23177,7 @@
       </c>
       <c r="H570" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23217,7 +23217,7 @@
       </c>
       <c r="H571" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23257,7 +23257,7 @@
       </c>
       <c r="H572" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23297,7 +23297,7 @@
       </c>
       <c r="H573" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23337,7 +23337,7 @@
       </c>
       <c r="H574" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23377,7 +23377,7 @@
       </c>
       <c r="H575" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23417,7 +23417,7 @@
       </c>
       <c r="H576" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="H577" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23497,7 +23497,7 @@
       </c>
       <c r="H578" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23537,7 +23537,7 @@
       </c>
       <c r="H579" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23577,7 +23577,7 @@
       </c>
       <c r="H580" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23617,7 +23617,7 @@
       </c>
       <c r="H581" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23657,7 +23657,7 @@
       </c>
       <c r="H582" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="H583" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23737,7 +23737,7 @@
       </c>
       <c r="H584" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="H585" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23817,7 +23817,7 @@
       </c>
       <c r="H586" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23857,7 +23857,7 @@
       </c>
       <c r="H587" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23897,7 +23897,7 @@
       </c>
       <c r="H588" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="H589" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -23977,7 +23977,7 @@
       </c>
       <c r="H590" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="H591" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24057,7 +24057,7 @@
       </c>
       <c r="H592" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24097,7 +24097,7 @@
       </c>
       <c r="H593" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24137,7 +24137,7 @@
       </c>
       <c r="H594" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24177,7 +24177,7 @@
       </c>
       <c r="H595" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H596" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24257,7 +24257,7 @@
       </c>
       <c r="H597" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24297,7 +24297,7 @@
       </c>
       <c r="H598" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24337,7 +24337,7 @@
       </c>
       <c r="H599" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24377,7 +24377,7 @@
       </c>
       <c r="H600" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="H601" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="H602" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="H603" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="H604" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="H605" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24617,7 +24617,7 @@
       </c>
       <c r="H606" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24657,7 +24657,7 @@
       </c>
       <c r="H607" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24697,7 +24697,7 @@
       </c>
       <c r="H608" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24737,7 +24737,7 @@
       </c>
       <c r="H609" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24777,7 +24777,7 @@
       </c>
       <c r="H610" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24817,7 +24817,7 @@
       </c>
       <c r="H611" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="H612" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24897,7 +24897,7 @@
       </c>
       <c r="H613" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24937,7 +24937,7 @@
       </c>
       <c r="H614" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -24977,7 +24977,7 @@
       </c>
       <c r="H615" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25017,7 +25017,7 @@
       </c>
       <c r="H616" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25057,7 +25057,7 @@
       </c>
       <c r="H617" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25097,7 +25097,7 @@
       </c>
       <c r="H618" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="H619" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25177,7 +25177,7 @@
       </c>
       <c r="H620" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="H621" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="H622" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25297,7 +25297,7 @@
       </c>
       <c r="H623" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25337,7 +25337,7 @@
       </c>
       <c r="H624" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25377,7 +25377,7 @@
       </c>
       <c r="H625" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25417,7 +25417,7 @@
       </c>
       <c r="H626" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25457,7 +25457,7 @@
       </c>
       <c r="H627" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="H628" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25537,7 +25537,7 @@
       </c>
       <c r="H629" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="H630" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25617,7 +25617,7 @@
       </c>
       <c r="H631" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25657,7 +25657,7 @@
       </c>
       <c r="H632" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25697,7 +25697,7 @@
       </c>
       <c r="H633" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25737,7 +25737,7 @@
       </c>
       <c r="H634" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25777,7 +25777,7 @@
       </c>
       <c r="H635" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25817,7 +25817,7 @@
       </c>
       <c r="H636" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25857,7 +25857,7 @@
       </c>
       <c r="H637" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25897,7 +25897,7 @@
       </c>
       <c r="H638" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="H639" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="H640" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26017,7 +26017,7 @@
       </c>
       <c r="H641" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="H642" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26097,7 +26097,7 @@
       </c>
       <c r="H643" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26137,7 +26137,7 @@
       </c>
       <c r="H644" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26177,7 +26177,7 @@
       </c>
       <c r="H645" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26217,7 +26217,7 @@
       </c>
       <c r="H646" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26257,7 +26257,7 @@
       </c>
       <c r="H647" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26297,7 +26297,7 @@
       </c>
       <c r="H648" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26337,7 +26337,7 @@
       </c>
       <c r="H649" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26377,7 +26377,7 @@
       </c>
       <c r="H650" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26417,7 +26417,7 @@
       </c>
       <c r="H651" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26457,7 +26457,7 @@
       </c>
       <c r="H652" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26497,7 +26497,7 @@
       </c>
       <c r="H653" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26537,7 +26537,7 @@
       </c>
       <c r="H654" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26577,7 +26577,7 @@
       </c>
       <c r="H655" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26617,7 +26617,7 @@
       </c>
       <c r="H656" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H657" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26697,7 +26697,7 @@
       </c>
       <c r="H658" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>
@@ -26737,7 +26737,7 @@
       </c>
       <c r="H659" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): Modal never opened: [data-testid='do-dealer-select'] absent after retry (trigger button: present,enabled=True,displayed=True; any modal-shaped overlay open: False; document.activeElement: BODY) (screenshot: OUT-004-round3.png)</t>
         </is>
       </c>
     </row>

--- a/docs/test/selenium_error.xlsx
+++ b/docs/test/selenium_error.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25 11:28:47</t>
+          <t>2026-07-26 00:17:57</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>147</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
@@ -22202,7 +22202,7 @@
       </c>
       <c r="E546" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F546" s="7" t="inlineStr">
@@ -22217,7 +22217,7 @@
       </c>
       <c r="H546" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22242,7 +22242,7 @@
       </c>
       <c r="E547" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F547" s="7" t="inlineStr">
@@ -22257,7 +22257,7 @@
       </c>
       <c r="H547" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22282,7 +22282,7 @@
       </c>
       <c r="E548" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F548" s="7" t="inlineStr">
@@ -22297,7 +22297,7 @@
       </c>
       <c r="H548" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22322,7 +22322,7 @@
       </c>
       <c r="E549" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F549" s="7" t="inlineStr">
@@ -22337,7 +22337,7 @@
       </c>
       <c r="H549" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22362,7 +22362,7 @@
       </c>
       <c r="E550" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F550" s="7" t="inlineStr">
@@ -22377,7 +22377,7 @@
       </c>
       <c r="H550" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22402,7 +22402,7 @@
       </c>
       <c r="E551" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F551" s="7" t="inlineStr">
@@ -22417,7 +22417,7 @@
       </c>
       <c r="H551" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22442,7 @@
       </c>
       <c r="E552" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F552" s="7" t="inlineStr">
@@ -22457,7 +22457,7 @@
       </c>
       <c r="H552" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="E553" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F553" s="7" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="H553" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22522,7 +22522,7 @@
       </c>
       <c r="E554" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F554" s="7" t="inlineStr">
@@ -22537,7 +22537,7 @@
       </c>
       <c r="H554" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22562,7 +22562,7 @@
       </c>
       <c r="E555" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F555" s="7" t="inlineStr">
@@ -22577,7 +22577,7 @@
       </c>
       <c r="H555" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22602,7 +22602,7 @@
       </c>
       <c r="E556" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F556" s="7" t="inlineStr">
@@ -22617,7 +22617,7 @@
       </c>
       <c r="H556" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22642,7 +22642,7 @@
       </c>
       <c r="E557" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F557" s="7" t="inlineStr">
@@ -22657,7 +22657,7 @@
       </c>
       <c r="H557" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="E558" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F558" s="7" t="inlineStr">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="H558" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22722,7 +22722,7 @@
       </c>
       <c r="E559" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F559" s="7" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="H559" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22762,7 +22762,7 @@
       </c>
       <c r="E560" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F560" s="7" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="H560" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22802,7 +22802,7 @@
       </c>
       <c r="E561" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F561" s="7" t="inlineStr">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="H561" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="E562" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F562" s="7" t="inlineStr">
@@ -22857,7 +22857,7 @@
       </c>
       <c r="H562" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="E563" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F563" s="7" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="H563" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22922,7 +22922,7 @@
       </c>
       <c r="E564" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F564" s="7" t="inlineStr">
@@ -22937,7 +22937,7 @@
       </c>
       <c r="H564" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -22962,7 +22962,7 @@
       </c>
       <c r="E565" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F565" s="7" t="inlineStr">
@@ -22977,7 +22977,7 @@
       </c>
       <c r="H565" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23002,7 +23002,7 @@
       </c>
       <c r="E566" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F566" s="7" t="inlineStr">
@@ -23017,7 +23017,7 @@
       </c>
       <c r="H566" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23042,7 +23042,7 @@
       </c>
       <c r="E567" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F567" s="7" t="inlineStr">
@@ -23057,7 +23057,7 @@
       </c>
       <c r="H567" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23082,7 +23082,7 @@
       </c>
       <c r="E568" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F568" s="7" t="inlineStr">
@@ -23097,7 +23097,7 @@
       </c>
       <c r="H568" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23122,7 +23122,7 @@
       </c>
       <c r="E569" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F569" s="7" t="inlineStr">
@@ -23137,7 +23137,7 @@
       </c>
       <c r="H569" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23162,7 +23162,7 @@
       </c>
       <c r="E570" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F570" s="7" t="inlineStr">
@@ -23177,7 +23177,7 @@
       </c>
       <c r="H570" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23202,7 +23202,7 @@
       </c>
       <c r="E571" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F571" s="7" t="inlineStr">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="H571" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23242,7 +23242,7 @@
       </c>
       <c r="E572" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F572" s="7" t="inlineStr">
@@ -23257,7 +23257,7 @@
       </c>
       <c r="H572" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="E573" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F573" s="7" t="inlineStr">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="H573" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23322,7 +23322,7 @@
       </c>
       <c r="E574" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F574" s="7" t="inlineStr">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="H574" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23362,7 +23362,7 @@
       </c>
       <c r="E575" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F575" s="7" t="inlineStr">
@@ -23377,7 +23377,7 @@
       </c>
       <c r="H575" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23402,7 +23402,7 @@
       </c>
       <c r="E576" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F576" s="7" t="inlineStr">
@@ -23417,7 +23417,7 @@
       </c>
       <c r="H576" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23442,7 +23442,7 @@
       </c>
       <c r="E577" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F577" s="7" t="inlineStr">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="H577" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23482,7 +23482,7 @@
       </c>
       <c r="E578" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F578" s="7" t="inlineStr">
@@ -23497,7 +23497,7 @@
       </c>
       <c r="H578" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23522,7 +23522,7 @@
       </c>
       <c r="E579" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F579" s="7" t="inlineStr">
@@ -23537,7 +23537,7 @@
       </c>
       <c r="H579" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="E580" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F580" s="7" t="inlineStr">
@@ -23577,7 +23577,7 @@
       </c>
       <c r="H580" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="E581" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F581" s="7" t="inlineStr">
@@ -23617,7 +23617,7 @@
       </c>
       <c r="H581" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23642,7 +23642,7 @@
       </c>
       <c r="E582" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F582" s="7" t="inlineStr">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="H582" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23682,7 +23682,7 @@
       </c>
       <c r="E583" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F583" s="7" t="inlineStr">
@@ -23697,7 +23697,7 @@
       </c>
       <c r="H583" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="E584" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F584" s="7" t="inlineStr">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="H584" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23762,7 +23762,7 @@
       </c>
       <c r="E585" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F585" s="7" t="inlineStr">
@@ -23777,7 +23777,7 @@
       </c>
       <c r="H585" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="E586" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F586" s="7" t="inlineStr">
@@ -23817,7 +23817,7 @@
       </c>
       <c r="H586" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="E587" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F587" s="7" t="inlineStr">
@@ -23857,7 +23857,7 @@
       </c>
       <c r="H587" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="E588" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F588" s="7" t="inlineStr">
@@ -23897,7 +23897,7 @@
       </c>
       <c r="H588" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23922,7 +23922,7 @@
       </c>
       <c r="E589" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F589" s="7" t="inlineStr">
@@ -23937,7 +23937,7 @@
       </c>
       <c r="H589" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -23962,7 +23962,7 @@
       </c>
       <c r="E590" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F590" s="7" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="H590" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24002,7 +24002,7 @@
       </c>
       <c r="E591" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F591" s="7" t="inlineStr">
@@ -24017,7 +24017,7 @@
       </c>
       <c r="H591" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24042,7 +24042,7 @@
       </c>
       <c r="E592" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F592" s="7" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="H592" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24082,7 +24082,7 @@
       </c>
       <c r="E593" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F593" s="7" t="inlineStr">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="H593" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24122,7 +24122,7 @@
       </c>
       <c r="E594" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F594" s="7" t="inlineStr">
@@ -24137,7 +24137,7 @@
       </c>
       <c r="H594" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24162,7 +24162,7 @@
       </c>
       <c r="E595" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F595" s="7" t="inlineStr">
@@ -24177,7 +24177,7 @@
       </c>
       <c r="H595" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24202,7 +24202,7 @@
       </c>
       <c r="E596" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F596" s="7" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H596" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24242,7 +24242,7 @@
       </c>
       <c r="E597" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F597" s="7" t="inlineStr">
@@ -24257,7 +24257,7 @@
       </c>
       <c r="H597" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24282,7 +24282,7 @@
       </c>
       <c r="E598" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F598" s="7" t="inlineStr">
@@ -24297,7 +24297,7 @@
       </c>
       <c r="H598" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24322,7 +24322,7 @@
       </c>
       <c r="E599" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F599" s="7" t="inlineStr">
@@ -24337,7 +24337,7 @@
       </c>
       <c r="H599" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24362,7 +24362,7 @@
       </c>
       <c r="E600" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F600" s="7" t="inlineStr">
@@ -24377,7 +24377,7 @@
       </c>
       <c r="H600" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="E601" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F601" s="7" t="inlineStr">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="H601" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24442,7 +24442,7 @@
       </c>
       <c r="E602" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F602" s="7" t="inlineStr">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="H602" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24482,7 +24482,7 @@
       </c>
       <c r="E603" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F603" s="7" t="inlineStr">
@@ -24497,7 +24497,7 @@
       </c>
       <c r="H603" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24522,7 +24522,7 @@
       </c>
       <c r="E604" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F604" s="7" t="inlineStr">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="H604" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24562,7 +24562,7 @@
       </c>
       <c r="E605" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F605" s="7" t="inlineStr">
@@ -24577,7 +24577,7 @@
       </c>
       <c r="H605" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24602,7 +24602,7 @@
       </c>
       <c r="E606" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F606" s="7" t="inlineStr">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="H606" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="E607" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F607" s="7" t="inlineStr">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="H607" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24682,7 +24682,7 @@
       </c>
       <c r="E608" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F608" s="7" t="inlineStr">
@@ -24697,7 +24697,7 @@
       </c>
       <c r="H608" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24722,7 +24722,7 @@
       </c>
       <c r="E609" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F609" s="7" t="inlineStr">
@@ -24737,7 +24737,7 @@
       </c>
       <c r="H609" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24762,7 +24762,7 @@
       </c>
       <c r="E610" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F610" s="7" t="inlineStr">
@@ -24777,7 +24777,7 @@
       </c>
       <c r="H610" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="E611" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F611" s="7" t="inlineStr">
@@ -24817,7 +24817,7 @@
       </c>
       <c r="H611" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24842,7 +24842,7 @@
       </c>
       <c r="E612" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F612" s="7" t="inlineStr">
@@ -24857,7 +24857,7 @@
       </c>
       <c r="H612" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24882,7 +24882,7 @@
       </c>
       <c r="E613" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F613" s="7" t="inlineStr">
@@ -24897,7 +24897,7 @@
       </c>
       <c r="H613" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24922,7 +24922,7 @@
       </c>
       <c r="E614" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F614" s="7" t="inlineStr">
@@ -24937,7 +24937,7 @@
       </c>
       <c r="H614" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -24962,7 +24962,7 @@
       </c>
       <c r="E615" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F615" s="7" t="inlineStr">
@@ -24977,7 +24977,7 @@
       </c>
       <c r="H615" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25002,7 +25002,7 @@
       </c>
       <c r="E616" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F616" s="7" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="H616" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25042,7 +25042,7 @@
       </c>
       <c r="E617" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F617" s="7" t="inlineStr">
@@ -25057,7 +25057,7 @@
       </c>
       <c r="H617" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25082,7 +25082,7 @@
       </c>
       <c r="E618" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F618" s="7" t="inlineStr">
@@ -25097,7 +25097,7 @@
       </c>
       <c r="H618" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="E619" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F619" s="7" t="inlineStr">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="H619" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25162,7 +25162,7 @@
       </c>
       <c r="E620" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F620" s="7" t="inlineStr">
@@ -25177,7 +25177,7 @@
       </c>
       <c r="H620" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25202,7 +25202,7 @@
       </c>
       <c r="E621" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F621" s="7" t="inlineStr">
@@ -25217,7 +25217,7 @@
       </c>
       <c r="H621" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25242,7 +25242,7 @@
       </c>
       <c r="E622" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F622" s="7" t="inlineStr">
@@ -25257,7 +25257,7 @@
       </c>
       <c r="H622" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25282,7 +25282,7 @@
       </c>
       <c r="E623" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F623" s="7" t="inlineStr">
@@ -25297,7 +25297,7 @@
       </c>
       <c r="H623" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25322,7 +25322,7 @@
       </c>
       <c r="E624" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F624" s="7" t="inlineStr">
@@ -25337,7 +25337,7 @@
       </c>
       <c r="H624" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25362,7 +25362,7 @@
       </c>
       <c r="E625" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F625" s="7" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="H625" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25402,7 +25402,7 @@
       </c>
       <c r="E626" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F626" s="7" t="inlineStr">
@@ -25417,7 +25417,7 @@
       </c>
       <c r="H626" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25442,7 +25442,7 @@
       </c>
       <c r="E627" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F627" s="7" t="inlineStr">
@@ -25457,7 +25457,7 @@
       </c>
       <c r="H627" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25482,7 +25482,7 @@
       </c>
       <c r="E628" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F628" s="7" t="inlineStr">
@@ -25497,7 +25497,7 @@
       </c>
       <c r="H628" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25522,7 +25522,7 @@
       </c>
       <c r="E629" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F629" s="7" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="H629" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25562,7 +25562,7 @@
       </c>
       <c r="E630" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F630" s="7" t="inlineStr">
@@ -25577,7 +25577,7 @@
       </c>
       <c r="H630" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25602,7 +25602,7 @@
       </c>
       <c r="E631" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F631" s="7" t="inlineStr">
@@ -25617,7 +25617,7 @@
       </c>
       <c r="H631" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25642,7 +25642,7 @@
       </c>
       <c r="E632" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F632" s="7" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="H632" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25682,7 +25682,7 @@
       </c>
       <c r="E633" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F633" s="7" t="inlineStr">
@@ -25697,7 +25697,7 @@
       </c>
       <c r="H633" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25722,7 +25722,7 @@
       </c>
       <c r="E634" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F634" s="7" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="H634" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25762,7 +25762,7 @@
       </c>
       <c r="E635" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F635" s="7" t="inlineStr">
@@ -25777,7 +25777,7 @@
       </c>
       <c r="H635" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25802,7 +25802,7 @@
       </c>
       <c r="E636" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F636" s="7" t="inlineStr">
@@ -25817,7 +25817,7 @@
       </c>
       <c r="H636" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25842,7 +25842,7 @@
       </c>
       <c r="E637" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F637" s="7" t="inlineStr">
@@ -25857,7 +25857,7 @@
       </c>
       <c r="H637" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="E638" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F638" s="7" t="inlineStr">
@@ -25897,7 +25897,7 @@
       </c>
       <c r="H638" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25922,7 +25922,7 @@
       </c>
       <c r="E639" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F639" s="7" t="inlineStr">
@@ -25937,7 +25937,7 @@
       </c>
       <c r="H639" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -25962,7 +25962,7 @@
       </c>
       <c r="E640" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F640" s="7" t="inlineStr">
@@ -25977,7 +25977,7 @@
       </c>
       <c r="H640" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26002,7 +26002,7 @@
       </c>
       <c r="E641" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F641" s="7" t="inlineStr">
@@ -26017,7 +26017,7 @@
       </c>
       <c r="H641" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26042,7 +26042,7 @@
       </c>
       <c r="E642" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F642" s="7" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="H642" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26082,7 +26082,7 @@
       </c>
       <c r="E643" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F643" s="7" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="H643" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26122,7 +26122,7 @@
       </c>
       <c r="E644" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F644" s="7" t="inlineStr">
@@ -26137,7 +26137,7 @@
       </c>
       <c r="H644" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26162,7 +26162,7 @@
       </c>
       <c r="E645" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F645" s="7" t="inlineStr">
@@ -26177,7 +26177,7 @@
       </c>
       <c r="H645" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26202,7 +26202,7 @@
       </c>
       <c r="E646" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F646" s="7" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="H646" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="E647" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F647" s="7" t="inlineStr">
@@ -26257,7 +26257,7 @@
       </c>
       <c r="H647" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="E648" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F648" s="7" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="H648" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26322,7 +26322,7 @@
       </c>
       <c r="E649" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F649" s="7" t="inlineStr">
@@ -26337,7 +26337,7 @@
       </c>
       <c r="H649" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26362,7 +26362,7 @@
       </c>
       <c r="E650" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F650" s="7" t="inlineStr">
@@ -26377,7 +26377,7 @@
       </c>
       <c r="H650" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26402,7 +26402,7 @@
       </c>
       <c r="E651" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F651" s="7" t="inlineStr">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="H651" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26442,7 +26442,7 @@
       </c>
       <c r="E652" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F652" s="7" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="H652" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26482,7 +26482,7 @@
       </c>
       <c r="E653" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F653" s="7" t="inlineStr">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="H653" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26522,7 +26522,7 @@
       </c>
       <c r="E654" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F654" s="7" t="inlineStr">
@@ -26537,7 +26537,7 @@
       </c>
       <c r="H654" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26562,7 +26562,7 @@
       </c>
       <c r="E655" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F655" s="7" t="inlineStr">
@@ -26577,7 +26577,7 @@
       </c>
       <c r="H655" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26602,7 +26602,7 @@
       </c>
       <c r="E656" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F656" s="7" t="inlineStr">
@@ -26617,7 +26617,7 @@
       </c>
       <c r="H656" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26642,7 +26642,7 @@
       </c>
       <c r="E657" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F657" s="7" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H657" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26682,7 +26682,7 @@
       </c>
       <c r="E658" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F658" s="7" t="inlineStr">
@@ -26697,7 +26697,7 @@
       </c>
       <c r="H658" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26722,7 +26722,7 @@
       </c>
       <c r="E659" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F659" s="7" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="H659" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26762,7 +26762,7 @@
       </c>
       <c r="E660" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F660" s="7" t="inlineStr">
@@ -26777,7 +26777,7 @@
       </c>
       <c r="H660" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26802,7 +26802,7 @@
       </c>
       <c r="E661" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F661" s="7" t="inlineStr">
@@ -26817,7 +26817,7 @@
       </c>
       <c r="H661" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26842,7 +26842,7 @@
       </c>
       <c r="E662" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F662" s="7" t="inlineStr">
@@ -26857,7 +26857,7 @@
       </c>
       <c r="H662" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26882,7 +26882,7 @@
       </c>
       <c r="E663" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F663" s="7" t="inlineStr">
@@ -26897,7 +26897,7 @@
       </c>
       <c r="H663" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="E664" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F664" s="7" t="inlineStr">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="H664" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -26962,7 +26962,7 @@
       </c>
       <c r="E665" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F665" s="7" t="inlineStr">
@@ -26977,7 +26977,7 @@
       </c>
       <c r="H665" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27002,7 +27002,7 @@
       </c>
       <c r="E666" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F666" s="7" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="H666" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27042,7 +27042,7 @@
       </c>
       <c r="E667" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F667" s="7" t="inlineStr">
@@ -27057,7 +27057,7 @@
       </c>
       <c r="H667" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27082,7 +27082,7 @@
       </c>
       <c r="E668" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F668" s="7" t="inlineStr">
@@ -27097,7 +27097,7 @@
       </c>
       <c r="H668" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27122,7 +27122,7 @@
       </c>
       <c r="E669" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F669" s="7" t="inlineStr">
@@ -27137,7 +27137,7 @@
       </c>
       <c r="H669" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27162,7 +27162,7 @@
       </c>
       <c r="E670" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F670" s="7" t="inlineStr">
@@ -27177,7 +27177,7 @@
       </c>
       <c r="H670" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="E671" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F671" s="7" t="inlineStr">
@@ -27217,7 +27217,7 @@
       </c>
       <c r="H671" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27242,7 +27242,7 @@
       </c>
       <c r="E672" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F672" s="7" t="inlineStr">
@@ -27257,7 +27257,7 @@
       </c>
       <c r="H672" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27282,7 +27282,7 @@
       </c>
       <c r="E673" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F673" s="7" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="H673" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27322,7 +27322,7 @@
       </c>
       <c r="E674" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F674" s="7" t="inlineStr">
@@ -27337,7 +27337,7 @@
       </c>
       <c r="H674" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27362,7 +27362,7 @@
       </c>
       <c r="E675" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F675" s="7" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="H675" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27402,7 +27402,7 @@
       </c>
       <c r="E676" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F676" s="7" t="inlineStr">
@@ -27417,7 +27417,7 @@
       </c>
       <c r="H676" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27442,7 +27442,7 @@
       </c>
       <c r="E677" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F677" s="7" t="inlineStr">
@@ -27457,7 +27457,7 @@
       </c>
       <c r="H677" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -27482,7 +27482,7 @@
       </c>
       <c r="E678" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F678" s="7" t="inlineStr">
@@ -27497,7 +27497,7 @@
       </c>
       <c r="H678" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (PLANNER role): Skipped: submit disabled -- no product with an APPROVED price entry exists for this warehouse yet (needs Kế toán trưởng approval first, outside PLANNER's role) | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/price-history?status=APPROVED&amp;warehouseId=1 - Failed to load resource: the server responded with a status of 403 (Forbidden); http://localhost:3001/api/v1/price-history/lookup?productId=70&amp;warehouseId=1&amp;date=2026-07-25 - Failed to load resource: the server responded with a status of 404 (Not Found) (screenshot: OUT-004-round3.png)</t>
+          <t>Selenium E2E real business flow (PLANNER role): ok</t>
         </is>
       </c>
     </row>
@@ -32840,9 +32840,9 @@
           <t>Get All Periods Success</t>
         </is>
       </c>
-      <c r="E812" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E812" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F812" s="7" t="inlineStr">
@@ -32857,12 +32857,7 @@
       </c>
       <c r="H812" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32885,9 +32880,9 @@
           <t>Create Period Success</t>
         </is>
       </c>
-      <c r="E813" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E813" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F813" s="7" t="inlineStr">
@@ -32902,12 +32897,7 @@
       </c>
       <c r="H813" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32930,9 +32920,9 @@
           <t>Close Period Success</t>
         </is>
       </c>
-      <c r="E814" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E814" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F814" s="7" t="inlineStr">
@@ -32947,12 +32937,7 @@
       </c>
       <c r="H814" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -32975,9 +32960,9 @@
           <t>Get Active Notifications Success</t>
         </is>
       </c>
-      <c r="E815" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E815" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F815" s="7" t="inlineStr">
@@ -32992,12 +32977,7 @@
       </c>
       <c r="H815" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33020,9 +33000,9 @@
           <t>Mark As Read Success</t>
         </is>
       </c>
-      <c r="E816" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E816" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F816" s="7" t="inlineStr">
@@ -33037,12 +33017,7 @@
       </c>
       <c r="H816" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33065,9 +33040,9 @@
           <t>Create Invoice Accountant Returns201</t>
         </is>
       </c>
-      <c r="E817" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E817" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F817" s="7" t="inlineStr">
@@ -33082,12 +33057,7 @@
       </c>
       <c r="H817" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33110,9 +33080,9 @@
           <t>Create Invoice Storekeeper Returns403</t>
         </is>
       </c>
-      <c r="E818" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E818" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F818" s="7" t="inlineStr">
@@ -33127,12 +33097,7 @@
       </c>
       <c r="H818" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33155,9 +33120,9 @@
           <t>Get Invoices Accountant Returns200</t>
         </is>
       </c>
-      <c r="E819" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E819" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F819" s="7" t="inlineStr">
@@ -33172,12 +33137,7 @@
       </c>
       <c r="H819" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33200,9 +33160,9 @@
           <t>Create Payment Receipt Accountant Returns201</t>
         </is>
       </c>
-      <c r="E820" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E820" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F820" s="7" t="inlineStr">
@@ -33217,12 +33177,7 @@
       </c>
       <c r="H820" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33245,9 +33200,9 @@
           <t>Create Payment Receipt Storekeeper Returns403</t>
         </is>
       </c>
-      <c r="E821" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E821" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F821" s="7" t="inlineStr">
@@ -33262,12 +33217,7 @@
       </c>
       <c r="H821" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33290,9 +33240,9 @@
           <t>Get Payment Receipts Accountant Returns200</t>
         </is>
       </c>
-      <c r="E822" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E822" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F822" s="7" t="inlineStr">
@@ -33307,12 +33257,7 @@
       </c>
       <c r="H822" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33335,9 +33280,9 @@
           <t>Scan Payment Receipt Success</t>
         </is>
       </c>
-      <c r="E823" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E823" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F823" s="7" t="inlineStr">
@@ -33352,12 +33297,7 @@
       </c>
       <c r="H823" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33380,9 +33320,9 @@
           <t>Scan Payment Receipt Invalid File Type</t>
         </is>
       </c>
-      <c r="E824" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E824" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F824" s="7" t="inlineStr">
@@ -33397,12 +33337,7 @@
       </c>
       <c r="H824" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33425,9 +33360,9 @@
           <t>Create Supplier Invoice Success</t>
         </is>
       </c>
-      <c r="E825" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E825" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F825" s="7" t="inlineStr">
@@ -33442,12 +33377,7 @@
       </c>
       <c r="H825" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33470,9 +33400,9 @@
           <t>Get Supplier Invoices Success</t>
         </is>
       </c>
-      <c r="E826" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E826" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F826" s="7" t="inlineStr">
@@ -33487,12 +33417,7 @@
       </c>
       <c r="H826" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33515,9 +33440,9 @@
           <t>Get Supplier Invoice By Id Success</t>
         </is>
       </c>
-      <c r="E827" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E827" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F827" s="7" t="inlineStr">
@@ -33532,12 +33457,7 @@
       </c>
       <c r="H827" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33560,9 +33480,9 @@
           <t>Create Supplier Payment Success</t>
         </is>
       </c>
-      <c r="E828" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E828" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F828" s="7" t="inlineStr">
@@ -33577,12 +33497,7 @@
       </c>
       <c r="H828" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33605,9 +33520,9 @@
           <t>Get Supplier Payments Success</t>
         </is>
       </c>
-      <c r="E829" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E829" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F829" s="7" t="inlineStr">
@@ -33622,12 +33537,7 @@
       </c>
       <c r="H829" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33650,9 +33560,9 @@
           <t>Scan Supplier Payment Ocr Success</t>
         </is>
       </c>
-      <c r="E830" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E830" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F830" s="7" t="inlineStr">
@@ -33667,12 +33577,7 @@
       </c>
       <c r="H830" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33695,9 +33600,9 @@
           <t>Close Period Succeeds When No Pending Documents Exist</t>
         </is>
       </c>
-      <c r="E831" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E831" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F831" s="7" t="inlineStr">
@@ -33712,12 +33617,7 @@
       </c>
       <c r="H831" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33740,9 +33640,9 @@
           <t>Close Period Reports Blocking Receipts With Sample Numbers</t>
         </is>
       </c>
-      <c r="E832" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E832" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F832" s="7" t="inlineStr">
@@ -33757,12 +33657,7 @@
       </c>
       <c r="H832" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33785,9 +33680,9 @@
           <t>Close Period Rejects Already Closed Period</t>
         </is>
       </c>
-      <c r="E833" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E833" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F833" s="7" t="inlineStr">
@@ -33802,12 +33697,7 @@
       </c>
       <c r="H833" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33830,9 +33720,9 @@
           <t>Create Invoice Success</t>
         </is>
       </c>
-      <c r="E834" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E834" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F834" s="7" t="inlineStr">
@@ -33847,12 +33737,7 @@
       </c>
       <c r="H834" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33875,9 +33760,9 @@
           <t>Create Invoice Includes Pod Evidence From Delivery</t>
         </is>
       </c>
-      <c r="E835" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E835" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F835" s="7" t="inlineStr">
@@ -33892,12 +33777,7 @@
       </c>
       <c r="H835" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33920,9 +33800,9 @@
           <t>Create Invoice Denied For Non Accountant</t>
         </is>
       </c>
-      <c r="E836" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E836" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F836" s="7" t="inlineStr">
@@ -33937,12 +33817,7 @@
       </c>
       <c r="H836" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -33965,9 +33840,9 @@
           <t>Create Invoice Delivery Order Not Found</t>
         </is>
       </c>
-      <c r="E837" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E837" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F837" s="7" t="inlineStr">
@@ -33982,12 +33857,7 @@
       </c>
       <c r="H837" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34010,9 +33880,9 @@
           <t>Create Payment Receipt Success Fully Paid Unlocks Credit</t>
         </is>
       </c>
-      <c r="E838" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E838" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F838" s="7" t="inlineStr">
@@ -34027,12 +33897,7 @@
       </c>
       <c r="H838" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34055,9 +33920,9 @@
           <t>Run Daily Overdue Hold Job Locks Dealer And Alerts Accountant Managers</t>
         </is>
       </c>
-      <c r="E839" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E839" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F839" s="7" t="inlineStr">
@@ -34072,12 +33937,7 @@
       </c>
       <c r="H839" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34100,9 +33960,9 @@
           <t>Create Payment Receipt Denied For Non Accountant</t>
         </is>
       </c>
-      <c r="E840" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E840" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F840" s="7" t="inlineStr">
@@ -34117,12 +33977,7 @@
       </c>
       <c r="H840" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34145,9 +34000,9 @@
           <t>Create Payment Receipt Invoice Already Paid</t>
         </is>
       </c>
-      <c r="E841" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E841" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F841" s="7" t="inlineStr">
@@ -34162,12 +34017,7 @@
       </c>
       <c r="H841" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34190,9 +34040,9 @@
           <t>Create Payment Receipt Amount Exceeds Remaining</t>
         </is>
       </c>
-      <c r="E842" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E842" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F842" s="7" t="inlineStr">
@@ -34207,12 +34057,7 @@
       </c>
       <c r="H842" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34235,9 +34080,9 @@
           <t>Create Supplier Invoice Success</t>
         </is>
       </c>
-      <c r="E843" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E843" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F843" s="7" t="inlineStr">
@@ -34252,12 +34097,7 @@
       </c>
       <c r="H843" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34280,9 +34120,9 @@
           <t>Create Supplier Invoice Fails When Receipt Not Completed</t>
         </is>
       </c>
-      <c r="E844" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E844" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F844" s="7" t="inlineStr">
@@ -34297,12 +34137,7 @@
       </c>
       <c r="H844" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34325,9 +34160,9 @@
           <t>Create Supplier Invoice Fails For Non Accountant</t>
         </is>
       </c>
-      <c r="E845" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E845" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F845" s="7" t="inlineStr">
@@ -34342,12 +34177,7 @@
       </c>
       <c r="H845" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34370,9 +34200,9 @@
           <t>Create Supplier Payment Success</t>
         </is>
       </c>
-      <c r="E846" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E846" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F846" s="7" t="inlineStr">
@@ -34387,12 +34217,7 @@
       </c>
       <c r="H846" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34415,9 +34240,9 @@
           <t>Scan Supplier Payment Ocr Success</t>
         </is>
       </c>
-      <c r="E847" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E847" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F847" s="7" t="inlineStr">
@@ -34432,12 +34257,7 @@
       </c>
       <c r="H847" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34460,9 +34280,9 @@
           <t>Scan Supplier Payment Ocr Empty File Fails</t>
         </is>
       </c>
-      <c r="E848" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E848" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F848" s="7" t="inlineStr">
@@ -34477,12 +34297,7 @@
       </c>
       <c r="H848" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34505,9 +34320,9 @@
           <t>Create For Confirmed Delivery Creates Invoice Lines And Increases Dealer Balance</t>
         </is>
       </c>
-      <c r="E849" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E849" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F849" s="7" t="inlineStr">
@@ -34522,12 +34337,7 @@
       </c>
       <c r="H849" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34550,9 +34360,9 @@
           <t>Create For Confirmed Delivery Sets Due Date Thirty Days After Issue Date</t>
         </is>
       </c>
-      <c r="E850" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E850" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F850" s="7" t="inlineStr">
@@ -34567,12 +34377,7 @@
       </c>
       <c r="H850" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34595,9 +34400,9 @@
           <t>Create For Confirmed Delivery Rejects Missing Unit Price</t>
         </is>
       </c>
-      <c r="E851" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E851" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F851" s="7" t="inlineStr">
@@ -34612,12 +34417,7 @@
       </c>
       <c r="H851" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34640,9 +34440,9 @@
           <t>Create For Confirmed Delivery Returns Existing Invoice Without Balance Mutation</t>
         </is>
       </c>
-      <c r="E852" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E852" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F852" s="7" t="inlineStr">
@@ -34657,12 +34457,7 @@
       </c>
       <c r="H852" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34685,9 +34480,9 @@
           <t>Create For Confirmed Delivery Rejects Partial Delivery</t>
         </is>
       </c>
-      <c r="E853" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E853" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F853" s="7" t="inlineStr">
@@ -34702,12 +34497,7 @@
       </c>
       <c r="H853" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34730,9 +34520,9 @@
           <t>Create For Confirmed Delivery Handles Unique Constraint Collision Idempotently</t>
         </is>
       </c>
-      <c r="E854" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E854" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F854" s="7" t="inlineStr">
@@ -34747,12 +34537,7 @@
       </c>
       <c r="H854" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34775,9 +34560,9 @@
           <t>Create For Confirmed Delivery Audit Contains Dealer Balance Before And After</t>
         </is>
       </c>
-      <c r="E855" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E855" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F855" s="7" t="inlineStr">
@@ -34792,12 +34577,7 @@
       </c>
       <c r="H855" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34820,9 +34600,9 @@
           <t>Create For Confirmed Delivery Sets Credit Hold When Balance Exceeds Limit</t>
         </is>
       </c>
-      <c r="E856" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E856" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F856" s="7" t="inlineStr">
@@ -34837,12 +34617,7 @@
       </c>
       <c r="H856" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34865,9 +34640,9 @@
           <t>Create For Confirmed Delivery Stamps Accounting Period And Archives Billing Notification</t>
         </is>
       </c>
-      <c r="E857" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E857" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F857" s="7" t="inlineStr">
@@ -34882,12 +34657,7 @@
       </c>
       <c r="H857" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34910,9 +34680,9 @@
           <t>Create Backfill Invoice Rejects Delivery Order Not Completed</t>
         </is>
       </c>
-      <c r="E858" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E858" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F858" s="7" t="inlineStr">
@@ -34927,12 +34697,7 @@
       </c>
       <c r="H858" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -34955,9 +34720,9 @@
           <t>Create Backfill Invoice Rejects When Invoice Already Exists</t>
         </is>
       </c>
-      <c r="E859" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E859" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F859" s="7" t="inlineStr">
@@ -34972,12 +34737,7 @@
       </c>
       <c r="H859" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -35000,9 +34760,9 @@
           <t>Create Backfill Invoice Creates Invoice For Completed Order</t>
         </is>
       </c>
-      <c r="E860" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E860" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F860" s="7" t="inlineStr">
@@ -35017,12 +34777,7 @@
       </c>
       <c r="H860" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -35045,9 +34800,9 @@
           <t>renders accounting periods list correctly</t>
         </is>
       </c>
-      <c r="E861" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E861" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F861" s="7" t="inlineStr">
@@ -35062,12 +34817,7 @@
       </c>
       <c r="H861" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -35090,9 +34840,9 @@
           <t>opens confirmation modal and closes period on confirm</t>
         </is>
       </c>
-      <c r="E862" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E862" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F862" s="7" t="inlineStr">
@@ -35107,12 +34857,7 @@
       </c>
       <c r="H862" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -35135,9 +34880,9 @@
           <t>renders SupplierInvoices page and displays notification worklist</t>
         </is>
       </c>
-      <c r="E863" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E863" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F863" s="7" t="inlineStr">
@@ -35152,12 +34897,7 @@
       </c>
       <c r="H863" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -35180,9 +34920,9 @@
           <t>switches to Hóa đơn Mua hàng tab</t>
         </is>
       </c>
-      <c r="E864" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E864" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F864" s="7" t="inlineStr">
@@ -35197,12 +34937,7 @@
       </c>
       <c r="H864" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -35225,9 +34960,9 @@
           <t>opens modal to create supplier invoice when clicking Lập Hóa đơn Mua</t>
         </is>
       </c>
-      <c r="E865" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E865" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F865" s="7" t="inlineStr">
@@ -35242,12 +34977,7 @@
       </c>
       <c r="H865" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -35270,9 +35000,9 @@
           <t>renders title and invoices section</t>
         </is>
       </c>
-      <c r="E866" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E866" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F866" s="7" t="inlineStr">
@@ -35287,12 +35017,7 @@
       </c>
       <c r="H866" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -35315,9 +35040,9 @@
           <t>switches to aging report tab</t>
         </is>
       </c>
-      <c r="E867" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E867" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F867" s="7" t="inlineStr">
@@ -35332,12 +35057,7 @@
       </c>
       <c r="H867" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -35360,9 +35080,9 @@
           <t>renders title, form and payment log table</t>
         </is>
       </c>
-      <c r="E868" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E868" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F868" s="7" t="inlineStr">
@@ -35377,12 +35097,7 @@
       </c>
       <c r="H868" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -35405,9 +35120,9 @@
           <t>allows clicking record new payment button</t>
         </is>
       </c>
-      <c r="E869" s="9" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="E869" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F869" s="7" t="inlineStr">
@@ -35422,12 +35137,7 @@
       </c>
       <c r="H869" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (ACCOUNTANT role): Error toast shown after submit: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/payment-receipts - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx 276:14 "Create AR payment failed:" AxiosError: OVERPAYMENT_EXCEEDS_INVOICE: OVERPAYMENT_EXCEEDS_INVOICE: Payment amount exceeds invoice remaining balance of 4000000.00
-    at settle (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1441:12)
-    at XMLHttpRequest.onloadend (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:1845:7)
-    at Axios.request (http://localhost:3001/node_modules/.vite/deps/axios.js?v=eeaa0ddc:2670:41)
-    at async Object.createPaymentReceipt (http://localhost:3001/src/services/finance.service.js:294:22)
-    at async handleSubmitPayment (http://localhost:3001/src/pages/Finance/DealerDebtInvoice.jsx:272:7) (screenshot: FIN-008-round3.png)</t>
+          <t>Selenium E2E real business flow (ACCOUNTANT role): ok</t>
         </is>
       </c>
     </row>
@@ -35467,7 +35177,7 @@
       </c>
       <c r="H870" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35507,7 +35217,7 @@
       </c>
       <c r="H871" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35547,7 +35257,7 @@
       </c>
       <c r="H872" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35587,7 +35297,7 @@
       </c>
       <c r="H873" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35627,7 +35337,7 @@
       </c>
       <c r="H874" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35667,7 +35377,7 @@
       </c>
       <c r="H875" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35707,7 +35417,7 @@
       </c>
       <c r="H876" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35747,7 +35457,7 @@
       </c>
       <c r="H877" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35787,7 +35497,7 @@
       </c>
       <c r="H878" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35827,7 +35537,7 @@
       </c>
       <c r="H879" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35867,7 +35577,7 @@
       </c>
       <c r="H880" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35907,7 +35617,7 @@
       </c>
       <c r="H881" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35657,7 @@
       </c>
       <c r="H882" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -35987,7 +35697,7 @@
       </c>
       <c r="H883" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36027,7 +35737,7 @@
       </c>
       <c r="H884" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36067,7 +35777,7 @@
       </c>
       <c r="H885" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36107,7 +35817,7 @@
       </c>
       <c r="H886" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36147,7 +35857,7 @@
       </c>
       <c r="H887" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36187,7 +35897,7 @@
       </c>
       <c r="H888" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36227,7 +35937,7 @@
       </c>
       <c r="H889" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36267,7 +35977,7 @@
       </c>
       <c r="H890" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36307,7 +36017,7 @@
       </c>
       <c r="H891" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36057,7 @@
       </c>
       <c r="H892" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36387,7 +36097,7 @@
       </c>
       <c r="H893" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36427,7 +36137,7 @@
       </c>
       <c r="H894" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36467,7 +36177,7 @@
       </c>
       <c r="H895" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36507,7 +36217,7 @@
       </c>
       <c r="H896" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36547,7 +36257,7 @@
       </c>
       <c r="H897" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36587,7 +36297,7 @@
       </c>
       <c r="H898" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36627,7 +36337,7 @@
       </c>
       <c r="H899" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36667,7 +36377,7 @@
       </c>
       <c r="H900" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36707,7 +36417,7 @@
       </c>
       <c r="H901" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36747,7 +36457,7 @@
       </c>
       <c r="H902" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36787,7 +36497,7 @@
       </c>
       <c r="H903" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36827,7 +36537,7 @@
       </c>
       <c r="H904" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36867,7 +36577,7 @@
       </c>
       <c r="H905" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36907,7 +36617,7 @@
       </c>
       <c r="H906" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36947,7 +36657,7 @@
       </c>
       <c r="H907" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -36987,7 +36697,7 @@
       </c>
       <c r="H908" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -37027,7 +36737,7 @@
       </c>
       <c r="H909" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -37067,7 +36777,7 @@
       </c>
       <c r="H910" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -37107,7 +36817,7 @@
       </c>
       <c r="H911" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -37147,7 +36857,7 @@
       </c>
       <c r="H912" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -37187,7 +36897,7 @@
       </c>
       <c r="H913" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -37227,7 +36937,7 @@
       </c>
       <c r="H914" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
@@ -37267,7 +36977,7 @@
       </c>
       <c r="H915" s="7" t="inlineStr">
         <is>
-          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
+          <t>Selenium E2E real business flow (STOREKEEPER role): Error toast shown after submit: BUSINESS_RULE_VIOLATION: RETURN_EXCEEDS_ORIGINAL_SALE: Total returned quantity (2) exceeds original sales quantity (1.00) for product ID 11 | Console errors: http://localhost:3001/favicon.ico - Failed to load resource: the server responded with a status of 404 (Not Found); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity); http://localhost:3001/api/v1/returns - Failed to load resource: the server responded with a status of 422 (Unprocessable Entity) (screenshot: RET-009-round3.png)</t>
         </is>
       </c>
     </row>
